--- a/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20232.xlsx
+++ b/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="287">
   <si>
     <t>Mat</t>
   </si>
@@ -82,604 +82,802 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
+    <t>ANDRES</t>
+  </si>
+  <si>
+    <t>BACILIO</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>COXCAHUA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
+    <t>GUERRERO</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>MATA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>PIMENTEL</t>
+  </si>
+  <si>
+    <t>QUIROGA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>SOSA</t>
+  </si>
+  <si>
+    <t>XALAMIHUA</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>CORDOVA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>RUGERIO</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
     <t>BUSTOS</t>
   </si>
   <si>
+    <t>CERONIO</t>
+  </si>
+  <si>
     <t>LARA</t>
   </si>
   <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
     <t>TEQUIHUATLE</t>
   </si>
   <si>
-    <t>BONOLA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
+    <t>ALTAMIRA</t>
+  </si>
+  <si>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>ESCOBEDO</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>FUENTES</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>PASTRANA</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>SEGURA</t>
+  </si>
+  <si>
+    <t>SILVESTRE</t>
   </si>
   <si>
     <t>TEXOCO</t>
   </si>
   <si>
+    <t>ANGEL</t>
+  </si>
+  <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>RIOS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
+  </si>
+  <si>
+    <t>ECHAVARRIA</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>OROZCO</t>
+  </si>
+  <si>
+    <t>SAAVEDRA</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>ARRIETA</t>
+  </si>
+  <si>
+    <t>BORBONIO</t>
+  </si>
+  <si>
+    <t>CARRASCO</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>GIL</t>
+  </si>
+  <si>
+    <t>IXTLA</t>
+  </si>
+  <si>
+    <t>MAY</t>
+  </si>
+  <si>
+    <t>MARIN</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>TLAXCALA</t>
+  </si>
+  <si>
+    <t>TENORIO</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>TETLA</t>
+  </si>
+  <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
+    <t>ATILANO</t>
+  </si>
+  <si>
+    <t>TZANAHUA</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>POOT</t>
+  </si>
+  <si>
+    <t>CANSECO</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>ENRIQUEZ</t>
+  </si>
+  <si>
+    <t>CAMACHO</t>
+  </si>
+  <si>
+    <t>FIGUEROA</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>YOPIHUA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>BACILIO</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
-    <t>GUERRERO</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>MATA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>PIMENTEL</t>
-  </si>
-  <si>
-    <t>QUIROGA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>SOSA</t>
-  </si>
-  <si>
-    <t>XALAMIHUA</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>ESCOBEDO</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>CERONIO</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>ALTAMIRA</t>
-  </si>
-  <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>FUENTES</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>PASTRANA</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>SILVESTRE</t>
-  </si>
-  <si>
-    <t>ANGEL</t>
-  </si>
-  <si>
-    <t>BONILLA</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>ECHAVARRIA</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>OROZCO</t>
-  </si>
-  <si>
-    <t>SAAVEDRA</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>NUBE</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
+    <t>VARILLAS</t>
+  </si>
+  <si>
+    <t>CARPINTEYRO</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>ALDUCIN</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>TELLEZ</t>
+  </si>
+  <si>
+    <t>TOLENTINO</t>
+  </si>
+  <si>
+    <t>NIEVES</t>
+  </si>
+  <si>
+    <t>TENCHIPE</t>
+  </si>
+  <si>
+    <t>CORREA</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>DURAND</t>
+  </si>
+  <si>
+    <t>PANZO</t>
+  </si>
+  <si>
+    <t>URBINA</t>
+  </si>
+  <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
+    <t>NAVA</t>
   </si>
   <si>
     <t>VASQUEZ</t>
   </si>
   <si>
-    <t>MIXTECO</t>
-  </si>
-  <si>
-    <t>NIEVES</t>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>MONTERROSA</t>
+  </si>
+  <si>
+    <t>HILARIO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
   </si>
   <si>
     <t>ANDRADE</t>
   </si>
   <si>
-    <t>TETLA</t>
-  </si>
-  <si>
-    <t>ATILANO</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>POOT</t>
-  </si>
-  <si>
-    <t>CANSECO</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>ENRIQUEZ</t>
-  </si>
-  <si>
-    <t>CAMACHO</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>FIGUEROA</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>VARILLAS</t>
-  </si>
-  <si>
-    <t>CARPINTEYRO</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>ALDUCIN</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>TELLEZ</t>
-  </si>
-  <si>
-    <t>TOLENTINO</t>
-  </si>
-  <si>
-    <t>TENCHIPE</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>DURAND</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>URBINA</t>
+    <t>ZOPIYACTLE</t>
+  </si>
+  <si>
+    <t>DECTOR</t>
+  </si>
+  <si>
+    <t>VIDAL</t>
+  </si>
+  <si>
+    <t>ARCOS</t>
+  </si>
+  <si>
+    <t>MANZANO</t>
+  </si>
+  <si>
+    <t>MIXCOA</t>
+  </si>
+  <si>
+    <t>TELE</t>
+  </si>
+  <si>
+    <t>SALINAS</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>KEVYN DANIEL</t>
+  </si>
+  <si>
+    <t>ANGEL CHARBEL</t>
+  </si>
+  <si>
+    <t>ALEX TADEO</t>
+  </si>
+  <si>
+    <t>ARELI DANAE</t>
+  </si>
+  <si>
+    <t>MIRANDA</t>
+  </si>
+  <si>
+    <t>HECTOR</t>
+  </si>
+  <si>
+    <t>JOSELYN</t>
+  </si>
+  <si>
+    <t>LEONARDO GABRIEL</t>
+  </si>
+  <si>
+    <t>DAVID</t>
+  </si>
+  <si>
+    <t>PAOLA</t>
+  </si>
+  <si>
+    <t>ARIADNA</t>
+  </si>
+  <si>
+    <t>MAR EDITH</t>
+  </si>
+  <si>
+    <t>MELISA</t>
+  </si>
+  <si>
+    <t>JUAN ALONSO</t>
+  </si>
+  <si>
+    <t>CRIZULY AMITHAI</t>
+  </si>
+  <si>
+    <t>ADIEL ALONSO</t>
+  </si>
+  <si>
+    <t>EUNICE</t>
+  </si>
+  <si>
+    <t>REYNA IVETT</t>
+  </si>
+  <si>
+    <t>ANDREA</t>
+  </si>
+  <si>
+    <t>HANNA MONTSERRAT</t>
+  </si>
+  <si>
+    <t>KAROL BALAAM</t>
+  </si>
+  <si>
+    <t>YASMIN</t>
+  </si>
+  <si>
+    <t>XIMENA ANALY</t>
+  </si>
+  <si>
+    <t>ROSA EVELYN</t>
+  </si>
+  <si>
+    <t>VANIA</t>
+  </si>
+  <si>
+    <t>DARLA AMERICA</t>
+  </si>
+  <si>
+    <t>SAMANTHA BETHANY</t>
+  </si>
+  <si>
+    <t>MARIEL BIDEMI</t>
+  </si>
+  <si>
+    <t>CARMEN VANELI</t>
+  </si>
+  <si>
+    <t>NAIDELYN</t>
+  </si>
+  <si>
+    <t>JOSE GUADALUPE</t>
+  </si>
+  <si>
+    <t>ANA KAREN</t>
+  </si>
+  <si>
+    <t>JOSE LUIS</t>
+  </si>
+  <si>
+    <t>LEONEL</t>
+  </si>
+  <si>
+    <t>EDUARDO</t>
+  </si>
+  <si>
+    <t>DANIA LIZETH</t>
+  </si>
+  <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
+    <t>MARITZA</t>
+  </si>
+  <si>
+    <t>MARYGELLI</t>
+  </si>
+  <si>
+    <t>MAGALY</t>
+  </si>
+  <si>
+    <t>JOCELYN</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
   </si>
   <si>
     <t>JOSE EMILIANO</t>
   </si>
   <si>
+    <t>JOSE ALDAIR</t>
+  </si>
+  <si>
     <t>DIEGO</t>
   </si>
   <si>
+    <t>ROBBIE ALONSO</t>
+  </si>
+  <si>
+    <t>ANTHONY</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
     <t>ISAAC</t>
   </si>
   <si>
-    <t>ANGEL NAIN</t>
-  </si>
-  <si>
-    <t>ANIELA SAMANTA</t>
-  </si>
-  <si>
-    <t>MIRANDA</t>
-  </si>
-  <si>
-    <t>MARGARITA</t>
-  </si>
-  <si>
-    <t>ALDO</t>
-  </si>
-  <si>
-    <t>GUADALUPE ANAHI</t>
+    <t>LINET</t>
+  </si>
+  <si>
+    <t>SAUL</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>OSWALDO</t>
+  </si>
+  <si>
+    <t>JANETH</t>
+  </si>
+  <si>
+    <t>ILSE JIMENA</t>
+  </si>
+  <si>
+    <t>DAYANA ASTRID</t>
+  </si>
+  <si>
+    <t>MARIAM MICHAELL</t>
+  </si>
+  <si>
+    <t>LAURA ISABEL</t>
+  </si>
+  <si>
+    <t>VIRIDIANA</t>
+  </si>
+  <si>
+    <t>YEIMI ALEXANDER</t>
+  </si>
+  <si>
+    <t>DIEGO GREGORIO</t>
+  </si>
+  <si>
+    <t>ANGEL EDUC</t>
+  </si>
+  <si>
+    <t>AXEL JOSUE</t>
+  </si>
+  <si>
+    <t>ANGELA</t>
+  </si>
+  <si>
+    <t>REY</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>CONCEPCION GUADALUPE</t>
+  </si>
+  <si>
+    <t>DAFNE</t>
+  </si>
+  <si>
+    <t>HEIDI</t>
+  </si>
+  <si>
+    <t>ARIADNA JARETZI</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL</t>
   </si>
   <si>
     <t>ESTRELLA ESMERALDA</t>
   </si>
   <si>
-    <t>XOCHITL ALELI</t>
-  </si>
-  <si>
-    <t>HECTOR</t>
+    <t>ESTRELLA RUBI</t>
+  </si>
+  <si>
+    <t>JAIR</t>
+  </si>
+  <si>
+    <t>DORIAN ALEXANDER</t>
+  </si>
+  <si>
+    <t>JUAN PABLO</t>
+  </si>
+  <si>
+    <t>KEIRA</t>
+  </si>
+  <si>
+    <t>URIEL</t>
+  </si>
+  <si>
+    <t>SALMA JANET</t>
+  </si>
+  <si>
+    <t>JESHUA</t>
+  </si>
+  <si>
+    <t>VICTOR JESUS</t>
   </si>
   <si>
     <t>ELIUD EDUARDO</t>
   </si>
   <si>
-    <t>DAVID</t>
-  </si>
-  <si>
-    <t>PAOLA</t>
-  </si>
-  <si>
-    <t>ARIADNA</t>
-  </si>
-  <si>
-    <t>MAR EDITH</t>
-  </si>
-  <si>
-    <t>MELISA</t>
-  </si>
-  <si>
-    <t>JUAN ALONSO</t>
-  </si>
-  <si>
-    <t>ADIEL ALONSO</t>
-  </si>
-  <si>
-    <t>EUNICE</t>
-  </si>
-  <si>
-    <t>REYNA IVETT</t>
-  </si>
-  <si>
-    <t>ANDREA</t>
-  </si>
-  <si>
-    <t>HANNA MONTSERRAT</t>
-  </si>
-  <si>
-    <t>KAROL BALAAM</t>
-  </si>
-  <si>
-    <t>YASMIN</t>
-  </si>
-  <si>
-    <t>ROSA EVELYN</t>
-  </si>
-  <si>
-    <t>VANIA</t>
-  </si>
-  <si>
-    <t>DARLA AMERICA</t>
-  </si>
-  <si>
-    <t>SAMANTHA BETHANY</t>
-  </si>
-  <si>
-    <t>MARIEL BIDEMI</t>
-  </si>
-  <si>
-    <t>CARMEN VANELI</t>
-  </si>
-  <si>
-    <t>NAIDELYN</t>
-  </si>
-  <si>
-    <t>JOSE GUADALUPE</t>
-  </si>
-  <si>
-    <t>ANA KAREN</t>
+    <t>KAORY AYELEN</t>
+  </si>
+  <si>
+    <t>MARIEL</t>
+  </si>
+  <si>
+    <t>JUAN CARLOS</t>
+  </si>
+  <si>
+    <t>ELIAS IGNACIO</t>
+  </si>
+  <si>
+    <t>KEVIN SANTIAGO</t>
   </si>
   <si>
     <t>JOSE EMMANUEL</t>
   </si>
   <si>
-    <t>JOSE LUIS</t>
-  </si>
-  <si>
-    <t>LEONEL</t>
+    <t>ANGEL GABRIEL</t>
+  </si>
+  <si>
+    <t>ALAN URIEL</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>JOANNA OCTAVIA</t>
   </si>
   <si>
     <t>IAN</t>
   </si>
   <si>
+    <t>JOSE ARTURO</t>
+  </si>
+  <si>
+    <t>ARELY SUSANA</t>
+  </si>
+  <si>
     <t>YAEL ISSAI</t>
   </si>
   <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>JOSE ALDAIR</t>
-  </si>
-  <si>
-    <t>ROBBIE ALONSO</t>
-  </si>
-  <si>
-    <t>ANTHONY</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>LINET</t>
-  </si>
-  <si>
-    <t>SAUL</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>OSWALDO</t>
-  </si>
-  <si>
-    <t>JANETH</t>
-  </si>
-  <si>
-    <t>ILSE JIMENA</t>
-  </si>
-  <si>
-    <t>DAYANA ASTRID</t>
-  </si>
-  <si>
-    <t>MARIAM MICHAELL</t>
-  </si>
-  <si>
-    <t>LAURA ISABEL</t>
-  </si>
-  <si>
-    <t>VIRIDIANA</t>
-  </si>
-  <si>
-    <t>YEIMI ALEXANDER</t>
-  </si>
-  <si>
-    <t>DIEGO GREGORIO</t>
-  </si>
-  <si>
-    <t>ANGEL EDUC</t>
-  </si>
-  <si>
-    <t>AXEL JOSUE</t>
-  </si>
-  <si>
-    <t>ANGELA</t>
-  </si>
-  <si>
-    <t>REY</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
+    <t>IRMA GUADALUPE</t>
+  </si>
+  <si>
+    <t>BRENDA</t>
+  </si>
+  <si>
+    <t>HELI AIMEE</t>
+  </si>
+  <si>
+    <t>AYLIN AMADA</t>
+  </si>
+  <si>
+    <t>JULIAN DAVID</t>
+  </si>
+  <si>
+    <t>CARLOS OCTAVIO</t>
+  </si>
+  <si>
+    <t>ANGELICA</t>
+  </si>
+  <si>
+    <t>ERNESTO</t>
+  </si>
+  <si>
+    <t>SINAI</t>
+  </si>
+  <si>
+    <t>ARANTZA NAHOMI</t>
+  </si>
+  <si>
+    <t>TATIANA</t>
+  </si>
+  <si>
+    <t>KENIA PAOLA</t>
+  </si>
+  <si>
+    <t>DIANA</t>
   </si>
   <si>
     <t>MELANY</t>
   </si>
   <si>
-    <t>CONCEPCION GUADALUPE</t>
-  </si>
-  <si>
-    <t>DAFNE</t>
-  </si>
-  <si>
-    <t>HEIDI</t>
-  </si>
-  <si>
-    <t>ARIADNA JARETZI</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>JAIR</t>
-  </si>
-  <si>
-    <t>JUAN PABLO</t>
-  </si>
-  <si>
-    <t>JOSELYN</t>
-  </si>
-  <si>
-    <t>KEIRA</t>
-  </si>
-  <si>
-    <t>URIEL</t>
-  </si>
-  <si>
-    <t>SALMA JANET</t>
-  </si>
-  <si>
-    <t>JESHUA</t>
-  </si>
-  <si>
-    <t>VICTOR JESUS</t>
-  </si>
-  <si>
-    <t>MARIEL</t>
-  </si>
-  <si>
-    <t>ELIAS IGNACIO</t>
-  </si>
-  <si>
-    <t>KEVIN SANTIAGO</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>ALAN URIEL</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>JOANNA OCTAVIA</t>
-  </si>
-  <si>
-    <t>JOSE ARTURO</t>
-  </si>
-  <si>
-    <t>ARELY SUSANA</t>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>MIRIAM NEFTALI</t>
+  </si>
+  <si>
+    <t>CINTHIA</t>
+  </si>
+  <si>
+    <t>ANGEL URIEL</t>
+  </si>
+  <si>
+    <t>MICHELLE</t>
+  </si>
+  <si>
+    <t>AXEL</t>
+  </si>
+  <si>
+    <t>LEYLA SARAI</t>
+  </si>
+  <si>
+    <t>LUZ MARIA</t>
+  </si>
+  <si>
+    <t>NOELIA</t>
+  </si>
+  <si>
+    <t>VERONICA</t>
   </si>
 </sst>
 </file>
@@ -1275,16 +1473,19 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>94.87</v>
+      </c>
+      <c r="H2">
+        <v>9.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1298,16 +1499,19 @@
         <v>31</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
         <v>31</v>
       </c>
-      <c r="E3">
-        <v>31</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
       <c r="G3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H3">
+        <v>8.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1321,16 +1525,19 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>91.43000000000001</v>
+      </c>
+      <c r="H4">
+        <v>8.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1367,16 +1574,19 @@
         <v>38</v>
       </c>
       <c r="D6">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>97.37</v>
+      </c>
+      <c r="H6">
+        <v>9.6</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1390,16 +1600,19 @@
         <v>30</v>
       </c>
       <c r="D7">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>80</v>
+      </c>
+      <c r="H7">
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -1586,7 +1799,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G126"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1618,16 +1831,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920180</v>
+        <v>23330051920185</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>54</v>
+        <v>108</v>
       </c>
       <c r="D2" t="s">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1641,16 +1854,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920199</v>
+        <v>23330051920192</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="D3" t="s">
-        <v>136</v>
+        <v>166</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1664,16 +1877,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920210</v>
+        <v>22330051920050</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>109</v>
       </c>
       <c r="D4" t="s">
-        <v>137</v>
+        <v>167</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1687,16 +1900,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920080</v>
+        <v>23330051920234</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="D5" t="s">
-        <v>138</v>
+        <v>168</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1710,16 +1923,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920261</v>
+        <v>23330051920103</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>139</v>
+        <v>169</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1739,10 +1952,10 @@
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D7" t="s">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1756,22 +1969,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920112</v>
+        <v>23330051920160</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="D8" t="s">
-        <v>141</v>
+        <v>171</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1779,22 +1992,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920114</v>
+        <v>23330051920161</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>58</v>
+        <v>112</v>
       </c>
       <c r="D9" t="s">
-        <v>142</v>
+        <v>172</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1802,22 +2015,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920115</v>
+        <v>23330051920166</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
-        <v>143</v>
+        <v>173</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1825,22 +2038,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920155</v>
+        <v>23330051920048</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="D11" t="s">
-        <v>144</v>
+        <v>174</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1848,22 +2061,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920325</v>
+        <v>23330051920050</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="D12" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1871,22 +2084,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920160</v>
+        <v>23330051920053</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="D13" t="s">
-        <v>146</v>
+        <v>176</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1894,22 +2107,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920354</v>
+        <v>23330051920054</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>147</v>
+        <v>177</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -1917,16 +2130,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920048</v>
+        <v>23330051920055</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>115</v>
       </c>
       <c r="D15" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1940,16 +2153,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920050</v>
+        <v>23330051920056</v>
       </c>
       <c r="B16" t="s">
         <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="D16" t="s">
-        <v>149</v>
+        <v>179</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1963,16 +2176,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920053</v>
+        <v>23330051920057</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>99</v>
+        <v>40</v>
       </c>
       <c r="D17" t="s">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1986,16 +2199,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920054</v>
+        <v>23330051920058</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="D18" t="s">
-        <v>151</v>
+        <v>181</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -2009,16 +2222,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>23330051920055</v>
+        <v>23330051920060</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>101</v>
+        <v>51</v>
       </c>
       <c r="D19" t="s">
-        <v>152</v>
+        <v>182</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -2032,16 +2245,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>23330051920056</v>
+        <v>23330051920061</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D20" t="s">
-        <v>153</v>
+        <v>183</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -2055,16 +2268,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>23330051920058</v>
+        <v>23330051920307</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="D21" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -2078,16 +2291,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>23330051920060</v>
+        <v>23330051920063</v>
       </c>
       <c r="B22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C22" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="D22" t="s">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -2101,16 +2314,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>23330051920061</v>
+        <v>23330051920064</v>
       </c>
       <c r="B23" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C23" t="s">
-        <v>103</v>
+        <v>46</v>
       </c>
       <c r="D23" t="s">
-        <v>156</v>
+        <v>186</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -2124,16 +2337,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>23330051920307</v>
+        <v>23330051920066</v>
       </c>
       <c r="B24" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C24" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="D24" t="s">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -2147,16 +2360,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>23330051920063</v>
+        <v>23330051920067</v>
       </c>
       <c r="B25" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C25" t="s">
-        <v>32</v>
+        <v>118</v>
       </c>
       <c r="D25" t="s">
-        <v>158</v>
+        <v>188</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -2170,16 +2383,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>23330051920064</v>
+        <v>23330051920068</v>
       </c>
       <c r="B26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C26" t="s">
-        <v>25</v>
+        <v>119</v>
       </c>
       <c r="D26" t="s">
-        <v>159</v>
+        <v>189</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -2193,16 +2406,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>23330051920066</v>
+        <v>23330051920069</v>
       </c>
       <c r="B27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="D27" t="s">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -2216,16 +2429,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>23330051920068</v>
+        <v>23330051920070</v>
       </c>
       <c r="B28" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C28" t="s">
-        <v>106</v>
+        <v>49</v>
       </c>
       <c r="D28" t="s">
-        <v>161</v>
+        <v>191</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -2239,16 +2452,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>23330051920069</v>
+        <v>23330051920272</v>
       </c>
       <c r="B29" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C29" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D29" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -2262,16 +2475,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>23330051920070</v>
+        <v>23330051920074</v>
       </c>
       <c r="B30" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C30" t="s">
-        <v>51</v>
+        <v>121</v>
       </c>
       <c r="D30" t="s">
-        <v>163</v>
+        <v>193</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -2285,16 +2498,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>23330051920272</v>
+        <v>23330051920075</v>
       </c>
       <c r="B31" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="C31" t="s">
-        <v>108</v>
+        <v>23</v>
       </c>
       <c r="D31" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -2308,22 +2521,22 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>23330051920074</v>
+        <v>23330051920029</v>
       </c>
       <c r="B32" t="s">
         <v>49</v>
       </c>
       <c r="C32" t="s">
-        <v>109</v>
+        <v>22</v>
       </c>
       <c r="D32" t="s">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
       </c>
       <c r="F32" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G32">
         <v>2</v>
@@ -2331,22 +2544,22 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>23330051920075</v>
+        <v>23330051920030</v>
       </c>
       <c r="B33" t="s">
         <v>50</v>
       </c>
       <c r="C33" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="D33" t="s">
-        <v>166</v>
+        <v>196</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
       </c>
       <c r="F33" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G33">
         <v>2</v>
@@ -2354,16 +2567,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>23330051920029</v>
+        <v>22330051920007</v>
       </c>
       <c r="B34" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C34" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D34" t="s">
-        <v>167</v>
+        <v>197</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -2377,16 +2590,16 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>23330051920030</v>
+        <v>23330051920035</v>
       </c>
       <c r="B35" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="C35" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="D35" t="s">
-        <v>168</v>
+        <v>198</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -2400,16 +2613,16 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>22330051920007</v>
+        <v>23330051920037</v>
       </c>
       <c r="B36" t="s">
         <v>51</v>
       </c>
       <c r="C36" t="s">
-        <v>31</v>
+        <v>124</v>
       </c>
       <c r="D36" t="s">
-        <v>169</v>
+        <v>199</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
@@ -2423,16 +2636,16 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>23330051920034</v>
+        <v>23330051920032</v>
       </c>
       <c r="B37" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C37" t="s">
-        <v>32</v>
+        <v>125</v>
       </c>
       <c r="D37" t="s">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
@@ -2446,22 +2659,22 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>23330051920035</v>
+        <v>23330051920133</v>
       </c>
       <c r="B38" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C38" t="s">
-        <v>111</v>
+        <v>42</v>
       </c>
       <c r="D38" t="s">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
       </c>
       <c r="F38" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G38">
         <v>2</v>
@@ -2469,22 +2682,22 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>23330051920037</v>
+        <v>23330051920122</v>
       </c>
       <c r="B39" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C39" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="D39" t="s">
-        <v>172</v>
+        <v>202</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
       </c>
       <c r="F39" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G39">
         <v>2</v>
@@ -2492,22 +2705,22 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>23330051920043</v>
+        <v>23330051920139</v>
       </c>
       <c r="B40" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="C40" t="s">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="D40" t="s">
-        <v>173</v>
+        <v>203</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
       </c>
       <c r="F40" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G40">
         <v>2</v>
@@ -2515,22 +2728,22 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>23330051920046</v>
+        <v>23330051920141</v>
       </c>
       <c r="B41" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C41" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="D41" t="s">
-        <v>174</v>
+        <v>204</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
       </c>
       <c r="F41" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G41">
         <v>2</v>
@@ -2538,62 +2751,62 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>23330051920179</v>
+        <v>23330051920145</v>
       </c>
       <c r="B42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C42" t="s">
-        <v>115</v>
+        <v>85</v>
       </c>
       <c r="D42" t="s">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
       </c>
       <c r="F42" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G42">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>23330051920182</v>
+        <v>23330051920150</v>
       </c>
       <c r="B43" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C43" t="s">
-        <v>116</v>
+        <v>25</v>
       </c>
       <c r="D43" t="s">
-        <v>176</v>
+        <v>206</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
       </c>
       <c r="F43" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G43">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>23330051920204</v>
+        <v>23330051920179</v>
       </c>
       <c r="B44" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C44" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="D44" t="s">
-        <v>177</v>
+        <v>207</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
@@ -2607,16 +2820,16 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>23330051920206</v>
+        <v>23330051920180</v>
       </c>
       <c r="B45" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C45" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="D45" t="s">
-        <v>178</v>
+        <v>208</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
@@ -2630,16 +2843,16 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>23330051920186</v>
+        <v>23330051920182</v>
       </c>
       <c r="B46" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C46" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="D46" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
@@ -2653,22 +2866,22 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
-        <v>23330051920078</v>
+        <v>23330051920199</v>
       </c>
       <c r="B47" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C47" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="D47" t="s">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
       </c>
       <c r="F47" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G47">
         <v>1</v>
@@ -2676,22 +2889,22 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48">
-        <v>23330051920077</v>
+        <v>23330051920204</v>
       </c>
       <c r="B48" t="s">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="C48" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="D48" t="s">
-        <v>181</v>
+        <v>211</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
       </c>
       <c r="F48" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G48">
         <v>1</v>
@@ -2699,22 +2912,22 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49">
-        <v>23330051920082</v>
+        <v>23330051920206</v>
       </c>
       <c r="B49" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C49" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="D49" t="s">
-        <v>182</v>
+        <v>212</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
       </c>
       <c r="F49" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G49">
         <v>1</v>
@@ -2722,22 +2935,22 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50">
-        <v>23330051920085</v>
+        <v>23330051920186</v>
       </c>
       <c r="B50" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="C50" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="D50" t="s">
-        <v>183</v>
+        <v>213</v>
       </c>
       <c r="E50" t="s">
         <v>8</v>
       </c>
       <c r="F50" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G50">
         <v>1</v>
@@ -2745,22 +2958,22 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51">
-        <v>23330051920086</v>
+        <v>23330051920210</v>
       </c>
       <c r="B51" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="C51" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D51" t="s">
-        <v>184</v>
+        <v>214</v>
       </c>
       <c r="E51" t="s">
         <v>8</v>
       </c>
       <c r="F51" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G51">
         <v>1</v>
@@ -2768,16 +2981,16 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52">
-        <v>23330051920084</v>
+        <v>23330051920078</v>
       </c>
       <c r="B52" t="s">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="C52" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D52" t="s">
-        <v>185</v>
+        <v>215</v>
       </c>
       <c r="E52" t="s">
         <v>8</v>
@@ -2791,16 +3004,16 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53">
-        <v>23330051920087</v>
+        <v>23330051920077</v>
       </c>
       <c r="B53" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="C53" t="s">
-        <v>31</v>
+        <v>132</v>
       </c>
       <c r="D53" t="s">
-        <v>186</v>
+        <v>216</v>
       </c>
       <c r="E53" t="s">
         <v>8</v>
@@ -2814,16 +3027,16 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54">
-        <v>23330051920088</v>
+        <v>23330051920082</v>
       </c>
       <c r="B54" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C54" t="s">
-        <v>58</v>
+        <v>133</v>
       </c>
       <c r="D54" t="s">
-        <v>187</v>
+        <v>217</v>
       </c>
       <c r="E54" t="s">
         <v>8</v>
@@ -2837,16 +3050,16 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55">
-        <v>23330051920089</v>
+        <v>23330051920085</v>
       </c>
       <c r="B55" t="s">
+        <v>21</v>
+      </c>
+      <c r="C55" t="s">
         <v>65</v>
       </c>
-      <c r="C55" t="s">
-        <v>40</v>
-      </c>
       <c r="D55" t="s">
-        <v>188</v>
+        <v>218</v>
       </c>
       <c r="E55" t="s">
         <v>8</v>
@@ -2860,16 +3073,16 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56">
-        <v>23330051920091</v>
+        <v>23330051920086</v>
       </c>
       <c r="B56" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="C56" t="s">
-        <v>99</v>
+        <v>61</v>
       </c>
       <c r="D56" t="s">
-        <v>189</v>
+        <v>219</v>
       </c>
       <c r="E56" t="s">
         <v>8</v>
@@ -2883,16 +3096,16 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57">
-        <v>23330051920094</v>
+        <v>23330051920084</v>
       </c>
       <c r="B57" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="C57" t="s">
-        <v>119</v>
+        <v>27</v>
       </c>
       <c r="D57" t="s">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="E57" t="s">
         <v>8</v>
@@ -2906,16 +3119,16 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58">
-        <v>23330051920251</v>
+        <v>23330051920087</v>
       </c>
       <c r="B58" t="s">
         <v>66</v>
       </c>
       <c r="C58" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D58" t="s">
-        <v>191</v>
+        <v>221</v>
       </c>
       <c r="E58" t="s">
         <v>8</v>
@@ -2929,16 +3142,16 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59">
-        <v>23330051920099</v>
+        <v>23330051920088</v>
       </c>
       <c r="B59" t="s">
         <v>67</v>
       </c>
       <c r="C59" t="s">
-        <v>120</v>
+        <v>25</v>
       </c>
       <c r="D59" t="s">
-        <v>192</v>
+        <v>222</v>
       </c>
       <c r="E59" t="s">
         <v>8</v>
@@ -2952,16 +3165,16 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60">
-        <v>23330051920098</v>
+        <v>23330051920089</v>
       </c>
       <c r="B60" t="s">
         <v>68</v>
       </c>
       <c r="C60" t="s">
-        <v>121</v>
+        <v>36</v>
       </c>
       <c r="D60" t="s">
-        <v>193</v>
+        <v>223</v>
       </c>
       <c r="E60" t="s">
         <v>8</v>
@@ -2975,16 +3188,16 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61">
-        <v>23330051920100</v>
+        <v>23330051920091</v>
       </c>
       <c r="B61" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="C61" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D61" t="s">
-        <v>194</v>
+        <v>224</v>
       </c>
       <c r="E61" t="s">
         <v>8</v>
@@ -2998,16 +3211,16 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62">
-        <v>23330051920102</v>
+        <v>23330051920094</v>
       </c>
       <c r="B62" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="C62" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="D62" t="s">
-        <v>195</v>
+        <v>225</v>
       </c>
       <c r="E62" t="s">
         <v>8</v>
@@ -3021,16 +3234,16 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63">
-        <v>23330051920104</v>
+        <v>23330051920251</v>
       </c>
       <c r="B63" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C63" t="s">
-        <v>124</v>
+        <v>27</v>
       </c>
       <c r="D63" t="s">
-        <v>196</v>
+        <v>226</v>
       </c>
       <c r="E63" t="s">
         <v>8</v>
@@ -3044,16 +3257,16 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64">
-        <v>23330051920105</v>
+        <v>23330051920099</v>
       </c>
       <c r="B64" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C64" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="D64" t="s">
-        <v>197</v>
+        <v>227</v>
       </c>
       <c r="E64" t="s">
         <v>8</v>
@@ -3067,16 +3280,16 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65">
-        <v>23330051920106</v>
+        <v>23330051920098</v>
       </c>
       <c r="B65" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C65" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="D65" t="s">
-        <v>198</v>
+        <v>228</v>
       </c>
       <c r="E65" t="s">
         <v>8</v>
@@ -3090,16 +3303,16 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66">
-        <v>23330051920108</v>
+        <v>23330051920100</v>
       </c>
       <c r="B66" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="C66" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="D66" t="s">
-        <v>199</v>
+        <v>229</v>
       </c>
       <c r="E66" t="s">
         <v>8</v>
@@ -3113,16 +3326,16 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67">
-        <v>23330051920110</v>
+        <v>23330051920102</v>
       </c>
       <c r="B67" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C67" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="D67" t="s">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="E67" t="s">
         <v>8</v>
@@ -3136,16 +3349,16 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68">
-        <v>23330051920111</v>
+        <v>23330051920104</v>
       </c>
       <c r="B68" t="s">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="C68" t="s">
-        <v>30</v>
+        <v>138</v>
       </c>
       <c r="D68" t="s">
-        <v>201</v>
+        <v>231</v>
       </c>
       <c r="E68" t="s">
         <v>8</v>
@@ -3159,22 +3372,22 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69">
-        <v>23330051920152</v>
+        <v>23330051920106</v>
       </c>
       <c r="B69" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C69" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="D69" t="s">
-        <v>202</v>
+        <v>232</v>
       </c>
       <c r="E69" t="s">
         <v>8</v>
       </c>
       <c r="F69" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G69">
         <v>1</v>
@@ -3182,22 +3395,22 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70">
-        <v>23330051920153</v>
+        <v>23330051920108</v>
       </c>
       <c r="B70" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C70" t="s">
-        <v>27</v>
+        <v>140</v>
       </c>
       <c r="D70" t="s">
-        <v>203</v>
+        <v>233</v>
       </c>
       <c r="E70" t="s">
         <v>8</v>
       </c>
       <c r="F70" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G70">
         <v>1</v>
@@ -3205,22 +3418,22 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71">
-        <v>23330051920157</v>
+        <v>23330051920110</v>
       </c>
       <c r="B71" t="s">
-        <v>32</v>
+        <v>76</v>
       </c>
       <c r="C71" t="s">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="D71" t="s">
-        <v>204</v>
+        <v>234</v>
       </c>
       <c r="E71" t="s">
         <v>8</v>
       </c>
       <c r="F71" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G71">
         <v>1</v>
@@ -3228,22 +3441,22 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72">
-        <v>23330051920159</v>
+        <v>23330051920111</v>
       </c>
       <c r="B72" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="C72" t="s">
-        <v>82</v>
+        <v>21</v>
       </c>
       <c r="D72" t="s">
-        <v>205</v>
+        <v>235</v>
       </c>
       <c r="E72" t="s">
         <v>8</v>
       </c>
       <c r="F72" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G72">
         <v>1</v>
@@ -3251,16 +3464,16 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73">
-        <v>23330051920161</v>
+        <v>23330051920152</v>
       </c>
       <c r="B73" t="s">
         <v>78</v>
       </c>
       <c r="C73" t="s">
-        <v>105</v>
+        <v>141</v>
       </c>
       <c r="D73" t="s">
-        <v>206</v>
+        <v>236</v>
       </c>
       <c r="E73" t="s">
         <v>8</v>
@@ -3274,16 +3487,16 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74">
-        <v>23330051920163</v>
+        <v>23330051920153</v>
       </c>
       <c r="B74" t="s">
         <v>79</v>
       </c>
       <c r="C74" t="s">
-        <v>129</v>
+        <v>77</v>
       </c>
       <c r="D74" t="s">
-        <v>207</v>
+        <v>237</v>
       </c>
       <c r="E74" t="s">
         <v>8</v>
@@ -3297,16 +3510,16 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75">
-        <v>23330051920297</v>
+        <v>23330051920155</v>
       </c>
       <c r="B75" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="C75" t="s">
-        <v>54</v>
+        <v>142</v>
       </c>
       <c r="D75" t="s">
-        <v>208</v>
+        <v>238</v>
       </c>
       <c r="E75" t="s">
         <v>8</v>
@@ -3320,16 +3533,16 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76">
-        <v>23330051920167</v>
+        <v>23330051920154</v>
       </c>
       <c r="B76" t="s">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="C76" t="s">
-        <v>25</v>
+        <v>142</v>
       </c>
       <c r="D76" t="s">
-        <v>209</v>
+        <v>239</v>
       </c>
       <c r="E76" t="s">
         <v>8</v>
@@ -3343,16 +3556,16 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77">
-        <v>23330051920310</v>
+        <v>23330051920250</v>
       </c>
       <c r="B77" t="s">
-        <v>81</v>
+        <v>22</v>
       </c>
       <c r="C77" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="D77" t="s">
-        <v>210</v>
+        <v>184</v>
       </c>
       <c r="E77" t="s">
         <v>8</v>
@@ -3366,16 +3579,16 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78">
-        <v>23330051920169</v>
+        <v>23330051920157</v>
       </c>
       <c r="B78" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C78" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="D78" t="s">
-        <v>211</v>
+        <v>240</v>
       </c>
       <c r="E78" t="s">
         <v>8</v>
@@ -3389,16 +3602,16 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79">
-        <v>23330051920173</v>
+        <v>23330051920158</v>
       </c>
       <c r="B79" t="s">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="C79" t="s">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="D79" t="s">
-        <v>212</v>
+        <v>241</v>
       </c>
       <c r="E79" t="s">
         <v>8</v>
@@ -3412,16 +3625,16 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80">
-        <v>23330051920172</v>
+        <v>23330051920159</v>
       </c>
       <c r="B80" t="s">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="C80" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="D80" t="s">
-        <v>182</v>
+        <v>242</v>
       </c>
       <c r="E80" t="s">
         <v>8</v>
@@ -3435,22 +3648,22 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81">
-        <v>23330051920031</v>
+        <v>23330051920163</v>
       </c>
       <c r="B81" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C81" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="D81" t="s">
-        <v>213</v>
+        <v>243</v>
       </c>
       <c r="E81" t="s">
         <v>8</v>
       </c>
       <c r="F81" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G81">
         <v>1</v>
@@ -3458,22 +3671,22 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82">
-        <v>23330051920033</v>
+        <v>23330051920297</v>
       </c>
       <c r="B82" t="s">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="C82" t="s">
-        <v>131</v>
+        <v>51</v>
       </c>
       <c r="D82" t="s">
-        <v>214</v>
+        <v>244</v>
       </c>
       <c r="E82" t="s">
         <v>8</v>
       </c>
       <c r="F82" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G82">
         <v>1</v>
@@ -3481,22 +3694,22 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83">
-        <v>23330051920232</v>
+        <v>23330051920167</v>
       </c>
       <c r="B83" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C83" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="D83" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="E83" t="s">
         <v>8</v>
       </c>
       <c r="F83" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G83">
         <v>1</v>
@@ -3504,22 +3717,22 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84">
-        <v>23330051920040</v>
+        <v>23330051920310</v>
       </c>
       <c r="B84" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C84" t="s">
-        <v>90</v>
+        <v>28</v>
       </c>
       <c r="D84" t="s">
-        <v>216</v>
+        <v>246</v>
       </c>
       <c r="E84" t="s">
         <v>8</v>
       </c>
       <c r="F84" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G84">
         <v>1</v>
@@ -3527,22 +3740,22 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85">
-        <v>23330051920041</v>
+        <v>23330051920169</v>
       </c>
       <c r="B85" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="C85" t="s">
-        <v>132</v>
+        <v>33</v>
       </c>
       <c r="D85" t="s">
-        <v>217</v>
+        <v>247</v>
       </c>
       <c r="E85" t="s">
         <v>8</v>
       </c>
       <c r="F85" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G85">
         <v>1</v>
@@ -3550,22 +3763,22 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86">
-        <v>23330051920042</v>
+        <v>23330051920354</v>
       </c>
       <c r="B86" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C86" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="D86" t="s">
-        <v>218</v>
+        <v>248</v>
       </c>
       <c r="E86" t="s">
         <v>8</v>
       </c>
       <c r="F86" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G86">
         <v>1</v>
@@ -3573,22 +3786,22 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87">
-        <v>23330051920044</v>
+        <v>23330051920170</v>
       </c>
       <c r="B87" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C87" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="D87" t="s">
-        <v>219</v>
+        <v>249</v>
       </c>
       <c r="E87" t="s">
         <v>8</v>
       </c>
       <c r="F87" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G87">
         <v>1</v>
@@ -3596,24 +3809,898 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88">
+        <v>23330051920173</v>
+      </c>
+      <c r="B88" t="s">
+        <v>85</v>
+      </c>
+      <c r="C88" t="s">
+        <v>34</v>
+      </c>
+      <c r="D88" t="s">
+        <v>250</v>
+      </c>
+      <c r="E88" t="s">
+        <v>8</v>
+      </c>
+      <c r="F88" t="s">
+        <v>10</v>
+      </c>
+      <c r="G88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7">
+      <c r="A89">
+        <v>23330051920172</v>
+      </c>
+      <c r="B89" t="s">
+        <v>86</v>
+      </c>
+      <c r="C89" t="s">
+        <v>51</v>
+      </c>
+      <c r="D89" t="s">
+        <v>217</v>
+      </c>
+      <c r="E89" t="s">
+        <v>8</v>
+      </c>
+      <c r="F89" t="s">
+        <v>10</v>
+      </c>
+      <c r="G89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7">
+      <c r="A90">
+        <v>23330051920174</v>
+      </c>
+      <c r="B90" t="s">
+        <v>87</v>
+      </c>
+      <c r="C90" t="s">
+        <v>87</v>
+      </c>
+      <c r="D90" t="s">
+        <v>251</v>
+      </c>
+      <c r="E90" t="s">
+        <v>8</v>
+      </c>
+      <c r="F90" t="s">
+        <v>10</v>
+      </c>
+      <c r="G90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7">
+      <c r="A91">
+        <v>23330051920031</v>
+      </c>
+      <c r="B91" t="s">
+        <v>88</v>
+      </c>
+      <c r="C91" t="s">
+        <v>145</v>
+      </c>
+      <c r="D91" t="s">
+        <v>252</v>
+      </c>
+      <c r="E91" t="s">
+        <v>8</v>
+      </c>
+      <c r="F91" t="s">
+        <v>12</v>
+      </c>
+      <c r="G91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7">
+      <c r="A92">
+        <v>23330051920033</v>
+      </c>
+      <c r="B92" t="s">
+        <v>89</v>
+      </c>
+      <c r="C92" t="s">
+        <v>146</v>
+      </c>
+      <c r="D92" t="s">
+        <v>253</v>
+      </c>
+      <c r="E92" t="s">
+        <v>8</v>
+      </c>
+      <c r="F92" t="s">
+        <v>12</v>
+      </c>
+      <c r="G92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7">
+      <c r="A93">
+        <v>23330051920034</v>
+      </c>
+      <c r="B93" t="s">
+        <v>66</v>
+      </c>
+      <c r="C93" t="s">
+        <v>27</v>
+      </c>
+      <c r="D93" t="s">
+        <v>254</v>
+      </c>
+      <c r="E93" t="s">
+        <v>8</v>
+      </c>
+      <c r="F93" t="s">
+        <v>12</v>
+      </c>
+      <c r="G93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7">
+      <c r="A94">
+        <v>23330051920232</v>
+      </c>
+      <c r="B94" t="s">
+        <v>90</v>
+      </c>
+      <c r="C94" t="s">
+        <v>21</v>
+      </c>
+      <c r="D94" t="s">
+        <v>255</v>
+      </c>
+      <c r="E94" t="s">
+        <v>8</v>
+      </c>
+      <c r="F94" t="s">
+        <v>12</v>
+      </c>
+      <c r="G94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7">
+      <c r="A95">
+        <v>23330051920040</v>
+      </c>
+      <c r="B95" t="s">
+        <v>91</v>
+      </c>
+      <c r="C95" t="s">
+        <v>94</v>
+      </c>
+      <c r="D95" t="s">
+        <v>256</v>
+      </c>
+      <c r="E95" t="s">
+        <v>8</v>
+      </c>
+      <c r="F95" t="s">
+        <v>12</v>
+      </c>
+      <c r="G95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7">
+      <c r="A96">
+        <v>23330051920041</v>
+      </c>
+      <c r="B96" t="s">
+        <v>70</v>
+      </c>
+      <c r="C96" t="s">
+        <v>147</v>
+      </c>
+      <c r="D96" t="s">
+        <v>257</v>
+      </c>
+      <c r="E96" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" t="s">
+        <v>12</v>
+      </c>
+      <c r="G96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7">
+      <c r="A97">
+        <v>23330051920042</v>
+      </c>
+      <c r="B97" t="s">
+        <v>92</v>
+      </c>
+      <c r="C97" t="s">
+        <v>21</v>
+      </c>
+      <c r="D97" t="s">
+        <v>258</v>
+      </c>
+      <c r="E97" t="s">
+        <v>8</v>
+      </c>
+      <c r="F97" t="s">
+        <v>12</v>
+      </c>
+      <c r="G97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7">
+      <c r="A98">
+        <v>23330051920043</v>
+      </c>
+      <c r="B98" t="s">
+        <v>46</v>
+      </c>
+      <c r="C98" t="s">
+        <v>130</v>
+      </c>
+      <c r="D98" t="s">
+        <v>259</v>
+      </c>
+      <c r="E98" t="s">
+        <v>8</v>
+      </c>
+      <c r="F98" t="s">
+        <v>12</v>
+      </c>
+      <c r="G98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7">
+      <c r="A99">
+        <v>23330051920044</v>
+      </c>
+      <c r="B99" t="s">
+        <v>93</v>
+      </c>
+      <c r="C99" t="s">
+        <v>24</v>
+      </c>
+      <c r="D99" t="s">
+        <v>260</v>
+      </c>
+      <c r="E99" t="s">
+        <v>8</v>
+      </c>
+      <c r="F99" t="s">
+        <v>12</v>
+      </c>
+      <c r="G99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7">
+      <c r="A100">
         <v>23330051920209</v>
       </c>
-      <c r="B88" t="s">
-        <v>90</v>
-      </c>
-      <c r="C88" t="s">
-        <v>134</v>
-      </c>
-      <c r="D88" t="s">
-        <v>220</v>
-      </c>
-      <c r="E88" t="s">
-        <v>8</v>
-      </c>
-      <c r="F88" t="s">
+      <c r="B100" t="s">
+        <v>94</v>
+      </c>
+      <c r="C100" t="s">
+        <v>148</v>
+      </c>
+      <c r="D100" t="s">
+        <v>261</v>
+      </c>
+      <c r="E100" t="s">
+        <v>8</v>
+      </c>
+      <c r="F100" t="s">
         <v>12</v>
       </c>
-      <c r="G88">
+      <c r="G100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7">
+      <c r="A101">
+        <v>23330051920046</v>
+      </c>
+      <c r="B101" t="s">
+        <v>95</v>
+      </c>
+      <c r="C101" t="s">
+        <v>149</v>
+      </c>
+      <c r="D101" t="s">
+        <v>262</v>
+      </c>
+      <c r="E101" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" t="s">
+        <v>12</v>
+      </c>
+      <c r="G101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7">
+      <c r="A102">
+        <v>23330051920117</v>
+      </c>
+      <c r="B102" t="s">
+        <v>96</v>
+      </c>
+      <c r="C102" t="s">
+        <v>150</v>
+      </c>
+      <c r="D102" t="s">
+        <v>263</v>
+      </c>
+      <c r="E102" t="s">
+        <v>8</v>
+      </c>
+      <c r="F102" t="s">
+        <v>13</v>
+      </c>
+      <c r="G102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7">
+      <c r="A103">
+        <v>23330061460223</v>
+      </c>
+      <c r="B103" t="s">
+        <v>97</v>
+      </c>
+      <c r="C103" t="s">
+        <v>151</v>
+      </c>
+      <c r="D103" t="s">
+        <v>264</v>
+      </c>
+      <c r="E103" t="s">
+        <v>8</v>
+      </c>
+      <c r="F103" t="s">
+        <v>13</v>
+      </c>
+      <c r="G103">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7">
+      <c r="A104">
+        <v>23330051920119</v>
+      </c>
+      <c r="B104" t="s">
+        <v>98</v>
+      </c>
+      <c r="C104" t="s">
+        <v>152</v>
+      </c>
+      <c r="D104" t="s">
+        <v>265</v>
+      </c>
+      <c r="E104" t="s">
+        <v>8</v>
+      </c>
+      <c r="F104" t="s">
+        <v>13</v>
+      </c>
+      <c r="G104">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7">
+      <c r="A105">
+        <v>23330051920120</v>
+      </c>
+      <c r="B105" t="s">
+        <v>99</v>
+      </c>
+      <c r="C105" t="s">
+        <v>52</v>
+      </c>
+      <c r="D105" t="s">
+        <v>266</v>
+      </c>
+      <c r="E105" t="s">
+        <v>8</v>
+      </c>
+      <c r="F105" t="s">
+        <v>13</v>
+      </c>
+      <c r="G105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7">
+      <c r="A106">
+        <v>23330051920121</v>
+      </c>
+      <c r="B106" t="s">
+        <v>100</v>
+      </c>
+      <c r="C106" t="s">
+        <v>153</v>
+      </c>
+      <c r="D106" t="s">
+        <v>175</v>
+      </c>
+      <c r="E106" t="s">
+        <v>8</v>
+      </c>
+      <c r="F106" t="s">
+        <v>13</v>
+      </c>
+      <c r="G106">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7">
+      <c r="A107">
+        <v>23330051920124</v>
+      </c>
+      <c r="B107" t="s">
+        <v>67</v>
+      </c>
+      <c r="C107" t="s">
+        <v>154</v>
+      </c>
+      <c r="D107" t="s">
+        <v>267</v>
+      </c>
+      <c r="E107" t="s">
+        <v>8</v>
+      </c>
+      <c r="F107" t="s">
+        <v>13</v>
+      </c>
+      <c r="G107">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7">
+      <c r="A108">
+        <v>23330051920125</v>
+      </c>
+      <c r="B108" t="s">
+        <v>22</v>
+      </c>
+      <c r="C108" t="s">
+        <v>155</v>
+      </c>
+      <c r="D108" t="s">
+        <v>268</v>
+      </c>
+      <c r="E108" t="s">
+        <v>8</v>
+      </c>
+      <c r="F108" t="s">
+        <v>13</v>
+      </c>
+      <c r="G108">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7">
+      <c r="A109">
+        <v>23330051920126</v>
+      </c>
+      <c r="B109" t="s">
+        <v>101</v>
+      </c>
+      <c r="C109" t="s">
+        <v>85</v>
+      </c>
+      <c r="D109" t="s">
+        <v>269</v>
+      </c>
+      <c r="E109" t="s">
+        <v>8</v>
+      </c>
+      <c r="F109" t="s">
+        <v>13</v>
+      </c>
+      <c r="G109">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7">
+      <c r="A110">
+        <v>23330051920127</v>
+      </c>
+      <c r="B110" t="s">
+        <v>27</v>
+      </c>
+      <c r="C110" t="s">
+        <v>156</v>
+      </c>
+      <c r="D110" t="s">
+        <v>270</v>
+      </c>
+      <c r="E110" t="s">
+        <v>8</v>
+      </c>
+      <c r="F110" t="s">
+        <v>13</v>
+      </c>
+      <c r="G110">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7">
+      <c r="A111">
+        <v>23330051920128</v>
+      </c>
+      <c r="B111" t="s">
+        <v>27</v>
+      </c>
+      <c r="C111" t="s">
+        <v>52</v>
+      </c>
+      <c r="D111" t="s">
+        <v>271</v>
+      </c>
+      <c r="E111" t="s">
+        <v>8</v>
+      </c>
+      <c r="F111" t="s">
+        <v>13</v>
+      </c>
+      <c r="G111">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7">
+      <c r="A112">
+        <v>23330051920129</v>
+      </c>
+      <c r="B112" t="s">
+        <v>27</v>
+      </c>
+      <c r="C112" t="s">
+        <v>71</v>
+      </c>
+      <c r="D112" t="s">
+        <v>272</v>
+      </c>
+      <c r="E112" t="s">
+        <v>8</v>
+      </c>
+      <c r="F112" t="s">
+        <v>13</v>
+      </c>
+      <c r="G112">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7">
+      <c r="A113">
+        <v>23330051920130</v>
+      </c>
+      <c r="B113" t="s">
+        <v>27</v>
+      </c>
+      <c r="C113" t="s">
+        <v>157</v>
+      </c>
+      <c r="D113" t="s">
+        <v>273</v>
+      </c>
+      <c r="E113" t="s">
+        <v>8</v>
+      </c>
+      <c r="F113" t="s">
+        <v>13</v>
+      </c>
+      <c r="G113">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7">
+      <c r="A114">
+        <v>23330051920134</v>
+      </c>
+      <c r="B114" t="s">
+        <v>51</v>
+      </c>
+      <c r="C114" t="s">
+        <v>27</v>
+      </c>
+      <c r="D114" t="s">
+        <v>274</v>
+      </c>
+      <c r="E114" t="s">
+        <v>8</v>
+      </c>
+      <c r="F114" t="s">
+        <v>13</v>
+      </c>
+      <c r="G114">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7">
+      <c r="A115">
+        <v>23330051920135</v>
+      </c>
+      <c r="B115" t="s">
+        <v>51</v>
+      </c>
+      <c r="C115" t="s">
+        <v>128</v>
+      </c>
+      <c r="D115" t="s">
+        <v>275</v>
+      </c>
+      <c r="E115" t="s">
+        <v>8</v>
+      </c>
+      <c r="F115" t="s">
+        <v>13</v>
+      </c>
+      <c r="G115">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7">
+      <c r="A116">
+        <v>23330051920137</v>
+      </c>
+      <c r="B116" t="s">
+        <v>102</v>
+      </c>
+      <c r="C116" t="s">
+        <v>158</v>
+      </c>
+      <c r="D116" t="s">
+        <v>276</v>
+      </c>
+      <c r="E116" t="s">
+        <v>8</v>
+      </c>
+      <c r="F116" t="s">
+        <v>13</v>
+      </c>
+      <c r="G116">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7">
+      <c r="A117">
+        <v>23330051920140</v>
+      </c>
+      <c r="B117" t="s">
+        <v>103</v>
+      </c>
+      <c r="C117" t="s">
+        <v>155</v>
+      </c>
+      <c r="D117" t="s">
+        <v>277</v>
+      </c>
+      <c r="E117" t="s">
+        <v>8</v>
+      </c>
+      <c r="F117" t="s">
+        <v>13</v>
+      </c>
+      <c r="G117">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7">
+      <c r="A118">
+        <v>23330051920138</v>
+      </c>
+      <c r="B118" t="s">
+        <v>104</v>
+      </c>
+      <c r="C118" t="s">
+        <v>159</v>
+      </c>
+      <c r="D118" t="s">
+        <v>278</v>
+      </c>
+      <c r="E118" t="s">
+        <v>8</v>
+      </c>
+      <c r="F118" t="s">
+        <v>13</v>
+      </c>
+      <c r="G118">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7">
+      <c r="A119">
+        <v>23330051920255</v>
+      </c>
+      <c r="B119" t="s">
+        <v>105</v>
+      </c>
+      <c r="C119" t="s">
+        <v>160</v>
+      </c>
+      <c r="D119" t="s">
+        <v>279</v>
+      </c>
+      <c r="E119" t="s">
+        <v>8</v>
+      </c>
+      <c r="F119" t="s">
+        <v>13</v>
+      </c>
+      <c r="G119">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7">
+      <c r="A120">
+        <v>23330051920315</v>
+      </c>
+      <c r="B120" t="s">
+        <v>45</v>
+      </c>
+      <c r="C120" t="s">
+        <v>161</v>
+      </c>
+      <c r="D120" t="s">
+        <v>280</v>
+      </c>
+      <c r="E120" t="s">
+        <v>8</v>
+      </c>
+      <c r="F120" t="s">
+        <v>13</v>
+      </c>
+      <c r="G120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7">
+      <c r="A121">
+        <v>23330051920143</v>
+      </c>
+      <c r="B121" t="s">
+        <v>46</v>
+      </c>
+      <c r="C121" t="s">
+        <v>162</v>
+      </c>
+      <c r="D121" t="s">
+        <v>281</v>
+      </c>
+      <c r="E121" t="s">
+        <v>8</v>
+      </c>
+      <c r="F121" t="s">
+        <v>13</v>
+      </c>
+      <c r="G121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7">
+      <c r="A122">
+        <v>23330051920144</v>
+      </c>
+      <c r="B122" t="s">
+        <v>60</v>
+      </c>
+      <c r="C122" t="s">
+        <v>60</v>
+      </c>
+      <c r="D122" t="s">
+        <v>282</v>
+      </c>
+      <c r="E122" t="s">
+        <v>8</v>
+      </c>
+      <c r="F122" t="s">
+        <v>13</v>
+      </c>
+      <c r="G122">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7">
+      <c r="A123">
+        <v>23330051920146</v>
+      </c>
+      <c r="B123" t="s">
+        <v>85</v>
+      </c>
+      <c r="C123" t="s">
+        <v>22</v>
+      </c>
+      <c r="D123" t="s">
+        <v>283</v>
+      </c>
+      <c r="E123" t="s">
+        <v>8</v>
+      </c>
+      <c r="F123" t="s">
+        <v>13</v>
+      </c>
+      <c r="G123">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7">
+      <c r="A124">
+        <v>23330051920147</v>
+      </c>
+      <c r="B124" t="s">
+        <v>94</v>
+      </c>
+      <c r="C124" t="s">
+        <v>163</v>
+      </c>
+      <c r="D124" t="s">
+        <v>284</v>
+      </c>
+      <c r="E124" t="s">
+        <v>8</v>
+      </c>
+      <c r="F124" t="s">
+        <v>13</v>
+      </c>
+      <c r="G124">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7">
+      <c r="A125">
+        <v>23330051920346</v>
+      </c>
+      <c r="B125" t="s">
+        <v>106</v>
+      </c>
+      <c r="C125" t="s">
+        <v>32</v>
+      </c>
+      <c r="D125" t="s">
+        <v>285</v>
+      </c>
+      <c r="E125" t="s">
+        <v>8</v>
+      </c>
+      <c r="F125" t="s">
+        <v>13</v>
+      </c>
+      <c r="G125">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7">
+      <c r="A126">
+        <v>23330051920149</v>
+      </c>
+      <c r="B126" t="s">
+        <v>107</v>
+      </c>
+      <c r="C126" t="s">
+        <v>164</v>
+      </c>
+      <c r="D126" t="s">
+        <v>286</v>
+      </c>
+      <c r="E126" t="s">
+        <v>8</v>
+      </c>
+      <c r="F126" t="s">
+        <v>13</v>
+      </c>
+      <c r="G126">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20232.xlsx
+++ b/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="291">
   <si>
     <t>Mat</t>
   </si>
@@ -109,15 +109,141 @@
     <t>MOLINA</t>
   </si>
   <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>CORDOVA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>RUGERIO</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>BUSTOS</t>
+  </si>
+  <si>
+    <t>CERONIO</t>
+  </si>
+  <si>
+    <t>LARA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
+    <t>ALTAMIRA</t>
+  </si>
+  <si>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>ESCOBEDO</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>FUENTES</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>PASTRANA</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>SEGURA</t>
+  </si>
+  <si>
+    <t>SILVESTRE</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>ANGEL</t>
+  </si>
+  <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>RIOS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
     <t>ANDRES</t>
   </si>
   <si>
     <t>BACILIO</t>
   </si>
   <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
     <t>COXCAHUA</t>
   </si>
   <si>
@@ -133,15 +259,9 @@
     <t>GUERRERO</t>
   </si>
   <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
     <t>MATA</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>PALOMARES</t>
   </si>
   <si>
@@ -166,183 +286,69 @@
     <t>XALAMIHUA</t>
   </si>
   <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>RUGERIO</t>
+    <t>COYOHUA</t>
+  </si>
+  <si>
+    <t>ECHAVARRIA</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>OROZCO</t>
+  </si>
+  <si>
+    <t>SAAVEDRA</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>ARRIETA</t>
+  </si>
+  <si>
+    <t>BORBONIO</t>
+  </si>
+  <si>
+    <t>CARRASCO</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>GIL</t>
+  </si>
+  <si>
+    <t>IXTLA</t>
+  </si>
+  <si>
+    <t>MAY</t>
+  </si>
+  <si>
+    <t>MARIN</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>TLAXCALA</t>
+  </si>
+  <si>
+    <t>TENORIO</t>
   </si>
   <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>BUSTOS</t>
-  </si>
-  <si>
-    <t>CERONIO</t>
-  </si>
-  <si>
-    <t>LARA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>ALTAMIRA</t>
-  </si>
-  <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>ESCOBEDO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>FUENTES</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>PASTRANA</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>SILVESTRE</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>ANGEL</t>
-  </si>
-  <si>
-    <t>BONILLA</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>RIOS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>ECHAVARRIA</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>OROZCO</t>
-  </si>
-  <si>
-    <t>SAAVEDRA</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>ARRIETA</t>
-  </si>
-  <si>
-    <t>BORBONIO</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>GIL</t>
-  </si>
-  <si>
-    <t>IXTLA</t>
-  </si>
-  <si>
-    <t>MAY</t>
-  </si>
-  <si>
-    <t>MARIN</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
-    <t>TENORIO</t>
-  </si>
-  <si>
     <t>COCOTLE</t>
   </si>
   <si>
@@ -358,12 +364,81 @@
     <t>AMADOR</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>VOTE</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>VARILLAS</t>
+  </si>
+  <si>
+    <t>CARPINTEYRO</t>
+  </si>
+  <si>
+    <t>TZANAHUA</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>ALDUCIN</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>TELLEZ</t>
+  </si>
+  <si>
+    <t>TOLENTINO</t>
+  </si>
+  <si>
+    <t>NIEVES</t>
+  </si>
+  <si>
+    <t>TENCHIPE</t>
+  </si>
+  <si>
+    <t>CORREA</t>
+  </si>
+  <si>
     <t>ATILANO</t>
   </si>
   <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
     <t>CORTES</t>
   </si>
   <si>
@@ -385,117 +460,48 @@
     <t>FIGUEROA</t>
   </si>
   <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>VERA</t>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>DURAND</t>
+  </si>
+  <si>
+    <t>PANZO</t>
+  </si>
+  <si>
+    <t>URBINA</t>
+  </si>
+  <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
+    <t>NAVA</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>MONTERROSA</t>
+  </si>
+  <si>
+    <t>HILARIO</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>ZOPIYACTLE</t>
+  </si>
+  <si>
+    <t>DECTOR</t>
   </si>
   <si>
     <t>VENTURA</t>
   </si>
   <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>VARILLAS</t>
-  </si>
-  <si>
-    <t>CARPINTEYRO</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>ALDUCIN</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>TELLEZ</t>
-  </si>
-  <si>
-    <t>TOLENTINO</t>
-  </si>
-  <si>
-    <t>NIEVES</t>
-  </si>
-  <si>
-    <t>TENCHIPE</t>
-  </si>
-  <si>
-    <t>CORREA</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>DURAND</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>URBINA</t>
-  </si>
-  <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
-    <t>NAVA</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>MONTERROSA</t>
-  </si>
-  <si>
-    <t>HILARIO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>ZOPIYACTLE</t>
-  </si>
-  <si>
-    <t>DECTOR</t>
-  </si>
-  <si>
     <t>VIDAL</t>
   </si>
   <si>
@@ -541,6 +547,180 @@
     <t>LEONARDO GABRIEL</t>
   </si>
   <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>DENISSE</t>
+  </si>
+  <si>
+    <t>NAIDELYN</t>
+  </si>
+  <si>
+    <t>JOSE GUADALUPE</t>
+  </si>
+  <si>
+    <t>ANA KAREN</t>
+  </si>
+  <si>
+    <t>JOSE LUIS</t>
+  </si>
+  <si>
+    <t>LEONEL</t>
+  </si>
+  <si>
+    <t>EDUARDO</t>
+  </si>
+  <si>
+    <t>CAMILO</t>
+  </si>
+  <si>
+    <t>DANIA LIZETH</t>
+  </si>
+  <si>
+    <t>MARITZA</t>
+  </si>
+  <si>
+    <t>MARYGELLI</t>
+  </si>
+  <si>
+    <t>MAGALY</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>JOSE EMILIANO</t>
+  </si>
+  <si>
+    <t>JOSE ALDAIR</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>ROBBIE ALONSO</t>
+  </si>
+  <si>
+    <t>ANTHONY</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>ISAAC</t>
+  </si>
+  <si>
+    <t>LINET</t>
+  </si>
+  <si>
+    <t>SAUL</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>OSWALDO</t>
+  </si>
+  <si>
+    <t>JANETH</t>
+  </si>
+  <si>
+    <t>ILSE JIMENA</t>
+  </si>
+  <si>
+    <t>DAYANA ASTRID</t>
+  </si>
+  <si>
+    <t>MARIAM MICHAELL</t>
+  </si>
+  <si>
+    <t>LAURA ISABEL</t>
+  </si>
+  <si>
+    <t>VIRIDIANA</t>
+  </si>
+  <si>
+    <t>YEIMI ALEXANDER</t>
+  </si>
+  <si>
+    <t>DIEGO GREGORIO</t>
+  </si>
+  <si>
+    <t>ANGEL EDUC</t>
+  </si>
+  <si>
+    <t>AXEL JOSUE</t>
+  </si>
+  <si>
+    <t>ANGELA</t>
+  </si>
+  <si>
+    <t>REY</t>
+  </si>
+  <si>
+    <t>CONCEPCION GUADALUPE</t>
+  </si>
+  <si>
+    <t>DAFNE</t>
+  </si>
+  <si>
+    <t>HEIDI</t>
+  </si>
+  <si>
+    <t>ARIADNA JARETZI</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>ESTRELLA ESMERALDA</t>
+  </si>
+  <si>
+    <t>ESTRELLA RUBI</t>
+  </si>
+  <si>
+    <t>ANDREA</t>
+  </si>
+  <si>
+    <t>JAIR</t>
+  </si>
+  <si>
+    <t>DORIAN ALEXANDER</t>
+  </si>
+  <si>
+    <t>JUAN PABLO</t>
+  </si>
+  <si>
+    <t>KEIRA</t>
+  </si>
+  <si>
+    <t>URIEL</t>
+  </si>
+  <si>
+    <t>SALMA JANET</t>
+  </si>
+  <si>
+    <t>JESHUA</t>
+  </si>
+  <si>
+    <t>VICTOR JESUS</t>
+  </si>
+  <si>
+    <t>ELIUD EDUARDO</t>
+  </si>
+  <si>
+    <t>KAORY AYELEN</t>
+  </si>
+  <si>
+    <t>MARIEL</t>
+  </si>
+  <si>
+    <t>JUAN CARLOS</t>
+  </si>
+  <si>
     <t>DAVID</t>
   </si>
   <si>
@@ -571,9 +751,6 @@
     <t>REYNA IVETT</t>
   </si>
   <si>
-    <t>ANDREA</t>
-  </si>
-  <si>
     <t>HANNA MONTSERRAT</t>
   </si>
   <si>
@@ -604,280 +781,115 @@
     <t>CARMEN VANELI</t>
   </si>
   <si>
-    <t>NAIDELYN</t>
-  </si>
-  <si>
-    <t>JOSE GUADALUPE</t>
-  </si>
-  <si>
-    <t>ANA KAREN</t>
-  </si>
-  <si>
-    <t>JOSE LUIS</t>
-  </si>
-  <si>
-    <t>LEONEL</t>
-  </si>
-  <si>
-    <t>EDUARDO</t>
-  </si>
-  <si>
-    <t>DANIA LIZETH</t>
+    <t>ELIAS IGNACIO</t>
+  </si>
+  <si>
+    <t>KEVIN SANTIAGO</t>
+  </si>
+  <si>
+    <t>JOSE EMMANUEL</t>
+  </si>
+  <si>
+    <t>ANGEL GABRIEL</t>
+  </si>
+  <si>
+    <t>ALAN URIEL</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>JOANNA OCTAVIA</t>
+  </si>
+  <si>
+    <t>IAN</t>
+  </si>
+  <si>
+    <t>JOSE ARTURO</t>
+  </si>
+  <si>
+    <t>ARELY SUSANA</t>
+  </si>
+  <si>
+    <t>YAEL ISSAI</t>
+  </si>
+  <si>
+    <t>IRMA GUADALUPE</t>
+  </si>
+  <si>
+    <t>BRENDA</t>
+  </si>
+  <si>
+    <t>HELI AIMEE</t>
+  </si>
+  <si>
+    <t>AYLIN AMADA</t>
+  </si>
+  <si>
+    <t>JULIAN DAVID</t>
+  </si>
+  <si>
+    <t>CARLOS OCTAVIO</t>
+  </si>
+  <si>
+    <t>ANGELICA</t>
+  </si>
+  <si>
+    <t>ERNESTO</t>
+  </si>
+  <si>
+    <t>SINAI</t>
+  </si>
+  <si>
+    <t>ARANTZA NAHOMI</t>
+  </si>
+  <si>
+    <t>TATIANA</t>
+  </si>
+  <si>
+    <t>KENIA PAOLA</t>
+  </si>
+  <si>
+    <t>DIANA</t>
+  </si>
+  <si>
+    <t>MELANY</t>
   </si>
   <si>
     <t>ABIGAIL</t>
   </si>
   <si>
-    <t>MARITZA</t>
-  </si>
-  <si>
-    <t>MARYGELLI</t>
-  </si>
-  <si>
-    <t>MAGALY</t>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>MIRIAM NEFTALI</t>
+  </si>
+  <si>
+    <t>CINTHIA</t>
+  </si>
+  <si>
+    <t>ANGEL URIEL</t>
+  </si>
+  <si>
+    <t>MICHELLE</t>
+  </si>
+  <si>
+    <t>AXEL</t>
+  </si>
+  <si>
+    <t>LEYLA SARAI</t>
+  </si>
+  <si>
+    <t>LUZ MARIA</t>
+  </si>
+  <si>
+    <t>NOELIA</t>
+  </si>
+  <si>
+    <t>VERONICA</t>
   </si>
   <si>
     <t>JOCELYN</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>JOSE EMILIANO</t>
-  </si>
-  <si>
-    <t>JOSE ALDAIR</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>ROBBIE ALONSO</t>
-  </si>
-  <si>
-    <t>ANTHONY</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>ISAAC</t>
-  </si>
-  <si>
-    <t>LINET</t>
-  </si>
-  <si>
-    <t>SAUL</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>OSWALDO</t>
-  </si>
-  <si>
-    <t>JANETH</t>
-  </si>
-  <si>
-    <t>ILSE JIMENA</t>
-  </si>
-  <si>
-    <t>DAYANA ASTRID</t>
-  </si>
-  <si>
-    <t>MARIAM MICHAELL</t>
-  </si>
-  <si>
-    <t>LAURA ISABEL</t>
-  </si>
-  <si>
-    <t>VIRIDIANA</t>
-  </si>
-  <si>
-    <t>YEIMI ALEXANDER</t>
-  </si>
-  <si>
-    <t>DIEGO GREGORIO</t>
-  </si>
-  <si>
-    <t>ANGEL EDUC</t>
-  </si>
-  <si>
-    <t>AXEL JOSUE</t>
-  </si>
-  <si>
-    <t>ANGELA</t>
-  </si>
-  <si>
-    <t>REY</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>CONCEPCION GUADALUPE</t>
-  </si>
-  <si>
-    <t>DAFNE</t>
-  </si>
-  <si>
-    <t>HEIDI</t>
-  </si>
-  <si>
-    <t>ARIADNA JARETZI</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>ESTRELLA ESMERALDA</t>
-  </si>
-  <si>
-    <t>ESTRELLA RUBI</t>
-  </si>
-  <si>
-    <t>JAIR</t>
-  </si>
-  <si>
-    <t>DORIAN ALEXANDER</t>
-  </si>
-  <si>
-    <t>JUAN PABLO</t>
-  </si>
-  <si>
-    <t>KEIRA</t>
-  </si>
-  <si>
-    <t>URIEL</t>
-  </si>
-  <si>
-    <t>SALMA JANET</t>
-  </si>
-  <si>
-    <t>JESHUA</t>
-  </si>
-  <si>
-    <t>VICTOR JESUS</t>
-  </si>
-  <si>
-    <t>ELIUD EDUARDO</t>
-  </si>
-  <si>
-    <t>KAORY AYELEN</t>
-  </si>
-  <si>
-    <t>MARIEL</t>
-  </si>
-  <si>
-    <t>JUAN CARLOS</t>
-  </si>
-  <si>
-    <t>ELIAS IGNACIO</t>
-  </si>
-  <si>
-    <t>KEVIN SANTIAGO</t>
-  </si>
-  <si>
-    <t>JOSE EMMANUEL</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>ALAN URIEL</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>JOANNA OCTAVIA</t>
-  </si>
-  <si>
-    <t>IAN</t>
-  </si>
-  <si>
-    <t>JOSE ARTURO</t>
-  </si>
-  <si>
-    <t>ARELY SUSANA</t>
-  </si>
-  <si>
-    <t>YAEL ISSAI</t>
-  </si>
-  <si>
-    <t>IRMA GUADALUPE</t>
-  </si>
-  <si>
-    <t>BRENDA</t>
-  </si>
-  <si>
-    <t>HELI AIMEE</t>
-  </si>
-  <si>
-    <t>AYLIN AMADA</t>
-  </si>
-  <si>
-    <t>JULIAN DAVID</t>
-  </si>
-  <si>
-    <t>CARLOS OCTAVIO</t>
-  </si>
-  <si>
-    <t>ANGELICA</t>
-  </si>
-  <si>
-    <t>ERNESTO</t>
-  </si>
-  <si>
-    <t>SINAI</t>
-  </si>
-  <si>
-    <t>ARANTZA NAHOMI</t>
-  </si>
-  <si>
-    <t>TATIANA</t>
-  </si>
-  <si>
-    <t>KENIA PAOLA</t>
-  </si>
-  <si>
-    <t>DIANA</t>
-  </si>
-  <si>
-    <t>MELANY</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MIRIAM NEFTALI</t>
-  </si>
-  <si>
-    <t>CINTHIA</t>
-  </si>
-  <si>
-    <t>ANGEL URIEL</t>
-  </si>
-  <si>
-    <t>MICHELLE</t>
-  </si>
-  <si>
-    <t>AXEL</t>
-  </si>
-  <si>
-    <t>LEYLA SARAI</t>
-  </si>
-  <si>
-    <t>LUZ MARIA</t>
-  </si>
-  <si>
-    <t>NOELIA</t>
-  </si>
-  <si>
-    <t>VERONICA</t>
   </si>
 </sst>
 </file>
@@ -1551,16 +1563,19 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>95.83</v>
+      </c>
+      <c r="H5">
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1799,7 +1814,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G126"/>
+  <dimension ref="A1:G129"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1837,10 +1852,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1860,10 +1875,10 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1883,10 +1898,10 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D4" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1906,10 +1921,10 @@
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1932,7 +1947,7 @@
         <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1952,10 +1967,10 @@
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="D7" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1975,10 +1990,10 @@
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D8" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1998,10 +2013,10 @@
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D9" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -2021,10 +2036,10 @@
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D10" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -2038,16 +2053,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920048</v>
+        <v>23330051920062</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -2061,16 +2076,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920050</v>
+        <v>23330051920065</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D12" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -2084,22 +2099,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920053</v>
+        <v>23330051920029</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>114</v>
+        <v>22</v>
       </c>
       <c r="D13" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -2107,22 +2122,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920054</v>
+        <v>23330051920030</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>23</v>
+        <v>116</v>
       </c>
       <c r="D14" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -2130,22 +2145,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920055</v>
+        <v>22330051920007</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>115</v>
+        <v>22</v>
       </c>
       <c r="D15" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G15">
         <v>2</v>
@@ -2153,22 +2168,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920056</v>
+        <v>23330051920035</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="D16" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -2176,22 +2191,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920057</v>
+        <v>23330051920037</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>40</v>
+        <v>117</v>
       </c>
       <c r="D17" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -2199,22 +2214,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920058</v>
+        <v>23330051920032</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D18" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G18">
         <v>2</v>
@@ -2222,22 +2237,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>23330051920060</v>
+        <v>22330061460232</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>51</v>
+        <v>119</v>
       </c>
       <c r="D19" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G19">
         <v>2</v>
@@ -2245,22 +2260,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>23330051920061</v>
+        <v>23330051920133</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C20" t="s">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="D20" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G20">
         <v>2</v>
@@ -2268,22 +2283,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>23330051920307</v>
+        <v>23330051920139</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C21" t="s">
-        <v>117</v>
+        <v>66</v>
       </c>
       <c r="D21" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G21">
         <v>2</v>
@@ -2291,22 +2306,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>23330051920063</v>
+        <v>23330051920141</v>
       </c>
       <c r="B22" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>120</v>
       </c>
       <c r="D22" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G22">
         <v>2</v>
@@ -2314,22 +2329,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>23330051920064</v>
+        <v>23330051920145</v>
       </c>
       <c r="B23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C23" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="D23" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G23">
         <v>2</v>
@@ -2337,482 +2352,482 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>23330051920066</v>
+        <v>23330051920179</v>
       </c>
       <c r="B24" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C24" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D24" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G24">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>23330051920067</v>
+        <v>23330051920180</v>
       </c>
       <c r="B25" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C25" t="s">
-        <v>118</v>
+        <v>34</v>
       </c>
       <c r="D25" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G25">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>23330051920068</v>
+        <v>23330051920182</v>
       </c>
       <c r="B26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C26" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D26" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G26">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>23330051920069</v>
+        <v>23330051920199</v>
       </c>
       <c r="B27" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C27" t="s">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="D27" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G27">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>23330051920070</v>
+        <v>23330051920204</v>
       </c>
       <c r="B28" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="C28" t="s">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="D28" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G28">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>23330051920272</v>
+        <v>23330051920206</v>
       </c>
       <c r="B29" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C29" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="D29" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
       </c>
       <c r="F29" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G29">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>23330051920074</v>
+        <v>23330051920186</v>
       </c>
       <c r="B30" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C30" t="s">
-        <v>121</v>
+        <v>23</v>
       </c>
       <c r="D30" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
       </c>
       <c r="F30" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G30">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>23330051920075</v>
+        <v>23330051920210</v>
       </c>
       <c r="B31" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C31" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="D31" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
       </c>
       <c r="F31" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G31">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>23330051920029</v>
+        <v>23330051920078</v>
       </c>
       <c r="B32" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C32" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D32" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
       </c>
       <c r="F32" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G32">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>23330051920030</v>
+        <v>23330051920077</v>
       </c>
       <c r="B33" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C33" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D33" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
       </c>
       <c r="F33" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G33">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>22330051920007</v>
+        <v>23330051920082</v>
       </c>
       <c r="B34" t="s">
         <v>49</v>
       </c>
       <c r="C34" t="s">
-        <v>22</v>
+        <v>126</v>
       </c>
       <c r="D34" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
       </c>
       <c r="F34" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G34">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>23330051920035</v>
+        <v>23330051920085</v>
       </c>
       <c r="B35" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C35" t="s">
-        <v>123</v>
+        <v>49</v>
       </c>
       <c r="D35" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
       </c>
       <c r="F35" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G35">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>23330051920037</v>
+        <v>23330051920086</v>
       </c>
       <c r="B36" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="C36" t="s">
-        <v>124</v>
+        <v>45</v>
       </c>
       <c r="D36" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
       </c>
       <c r="F36" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G36">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>23330051920032</v>
+        <v>23330051920084</v>
       </c>
       <c r="B37" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C37" t="s">
-        <v>125</v>
+        <v>27</v>
       </c>
       <c r="D37" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
       </c>
       <c r="F37" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G37">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>23330051920133</v>
+        <v>23330051920087</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="C38" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="D38" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
       </c>
       <c r="F38" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G38">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>23330051920122</v>
+        <v>23330051920088</v>
       </c>
       <c r="B39" t="s">
         <v>52</v>
       </c>
       <c r="C39" t="s">
-        <v>126</v>
+        <v>25</v>
       </c>
       <c r="D39" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
       </c>
       <c r="F39" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G39">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>23330051920139</v>
+        <v>23330051920089</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C40" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D40" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
       </c>
       <c r="F40" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G40">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>23330051920141</v>
+        <v>23330051920091</v>
       </c>
       <c r="B41" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="C41" t="s">
         <v>127</v>
       </c>
       <c r="D41" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
       </c>
       <c r="F41" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G41">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>23330051920145</v>
+        <v>23330051920094</v>
       </c>
       <c r="B42" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="C42" t="s">
-        <v>85</v>
+        <v>128</v>
       </c>
       <c r="D42" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
       </c>
       <c r="F42" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G42">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>23330051920150</v>
+        <v>23330051920251</v>
       </c>
       <c r="B43" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C43" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D43" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
       </c>
       <c r="F43" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G43">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>23330051920179</v>
+        <v>23330051920099</v>
       </c>
       <c r="B44" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C44" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D44" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
       </c>
       <c r="F44" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G44">
         <v>1</v>
@@ -2820,22 +2835,22 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>23330051920180</v>
+        <v>23330051920098</v>
       </c>
       <c r="B45" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C45" t="s">
-        <v>51</v>
+        <v>130</v>
       </c>
       <c r="D45" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
       </c>
       <c r="F45" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G45">
         <v>1</v>
@@ -2843,22 +2858,22 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>23330051920182</v>
+        <v>23330051920100</v>
       </c>
       <c r="B46" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="C46" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D46" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
       </c>
       <c r="F46" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G46">
         <v>1</v>
@@ -2866,22 +2881,22 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
-        <v>23330051920199</v>
+        <v>23330051920102</v>
       </c>
       <c r="B47" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C47" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="D47" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
       </c>
       <c r="F47" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G47">
         <v>1</v>
@@ -2889,22 +2904,22 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48">
-        <v>23330051920204</v>
+        <v>23330051920104</v>
       </c>
       <c r="B48" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="C48" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D48" t="s">
-        <v>211</v>
+        <v>176</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
       </c>
       <c r="F48" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G48">
         <v>1</v>
@@ -2912,22 +2927,22 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49">
-        <v>23330051920206</v>
+        <v>23330051920106</v>
       </c>
       <c r="B49" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C49" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D49" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
       </c>
       <c r="F49" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G49">
         <v>1</v>
@@ -2935,22 +2950,22 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50">
-        <v>23330051920186</v>
+        <v>23330051920108</v>
       </c>
       <c r="B50" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C50" t="s">
-        <v>23</v>
+        <v>134</v>
       </c>
       <c r="D50" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E50" t="s">
         <v>8</v>
       </c>
       <c r="F50" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G50">
         <v>1</v>
@@ -2958,22 +2973,22 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51">
-        <v>23330051920210</v>
+        <v>23330051920110</v>
       </c>
       <c r="B51" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C51" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="D51" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E51" t="s">
         <v>8</v>
       </c>
       <c r="F51" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G51">
         <v>1</v>
@@ -2981,16 +2996,16 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52">
-        <v>23330051920078</v>
+        <v>23330051920111</v>
       </c>
       <c r="B52" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C52" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D52" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E52" t="s">
         <v>8</v>
@@ -3004,22 +3019,22 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53">
-        <v>23330051920077</v>
+        <v>23330051920152</v>
       </c>
       <c r="B53" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C53" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D53" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E53" t="s">
         <v>8</v>
       </c>
       <c r="F53" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G53">
         <v>1</v>
@@ -3027,22 +3042,22 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54">
-        <v>23330051920082</v>
+        <v>23330051920153</v>
       </c>
       <c r="B54" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C54" t="s">
-        <v>133</v>
+        <v>62</v>
       </c>
       <c r="D54" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E54" t="s">
         <v>8</v>
       </c>
       <c r="F54" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G54">
         <v>1</v>
@@ -3050,22 +3065,22 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55">
-        <v>23330051920085</v>
+        <v>23330051920155</v>
       </c>
       <c r="B55" t="s">
         <v>21</v>
       </c>
       <c r="C55" t="s">
-        <v>65</v>
+        <v>136</v>
       </c>
       <c r="D55" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E55" t="s">
         <v>8</v>
       </c>
       <c r="F55" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G55">
         <v>1</v>
@@ -3073,22 +3088,22 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56">
-        <v>23330051920086</v>
+        <v>23330051920154</v>
       </c>
       <c r="B56" t="s">
         <v>21</v>
       </c>
       <c r="C56" t="s">
-        <v>61</v>
+        <v>136</v>
       </c>
       <c r="D56" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E56" t="s">
         <v>8</v>
       </c>
       <c r="F56" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G56">
         <v>1</v>
@@ -3096,22 +3111,22 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57">
-        <v>23330051920084</v>
+        <v>23330051920250</v>
       </c>
       <c r="B57" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C57" t="s">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="D57" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E57" t="s">
         <v>8</v>
       </c>
       <c r="F57" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G57">
         <v>1</v>
@@ -3119,22 +3134,22 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58">
-        <v>23330051920087</v>
+        <v>23330051920157</v>
       </c>
       <c r="B58" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="C58" t="s">
-        <v>22</v>
+        <v>86</v>
       </c>
       <c r="D58" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E58" t="s">
         <v>8</v>
       </c>
       <c r="F58" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G58">
         <v>1</v>
@@ -3142,22 +3157,22 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59">
-        <v>23330051920088</v>
+        <v>23330051920158</v>
       </c>
       <c r="B59" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="C59" t="s">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="D59" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E59" t="s">
         <v>8</v>
       </c>
       <c r="F59" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G59">
         <v>1</v>
@@ -3165,22 +3180,22 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60">
-        <v>23330051920089</v>
+        <v>23330051920159</v>
       </c>
       <c r="B60" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="C60" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="D60" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E60" t="s">
         <v>8</v>
       </c>
       <c r="F60" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G60">
         <v>1</v>
@@ -3188,22 +3203,22 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61">
-        <v>23330051920091</v>
+        <v>23330051920163</v>
       </c>
       <c r="B61" t="s">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="C61" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="D61" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E61" t="s">
         <v>8</v>
       </c>
       <c r="F61" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G61">
         <v>1</v>
@@ -3211,22 +3226,22 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62">
-        <v>23330051920094</v>
+        <v>23330051920297</v>
       </c>
       <c r="B62" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="C62" t="s">
-        <v>134</v>
+        <v>34</v>
       </c>
       <c r="D62" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E62" t="s">
         <v>8</v>
       </c>
       <c r="F62" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -3234,22 +3249,22 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63">
-        <v>23330051920251</v>
+        <v>23330051920167</v>
       </c>
       <c r="B63" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C63" t="s">
-        <v>27</v>
+        <v>86</v>
       </c>
       <c r="D63" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E63" t="s">
         <v>8</v>
       </c>
       <c r="F63" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G63">
         <v>1</v>
@@ -3257,22 +3272,22 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64">
-        <v>23330051920099</v>
+        <v>23330051920310</v>
       </c>
       <c r="B64" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C64" t="s">
-        <v>135</v>
+        <v>28</v>
       </c>
       <c r="D64" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E64" t="s">
         <v>8</v>
       </c>
       <c r="F64" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G64">
         <v>1</v>
@@ -3280,22 +3295,22 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65">
-        <v>23330051920098</v>
+        <v>23330051920169</v>
       </c>
       <c r="B65" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C65" t="s">
-        <v>136</v>
+        <v>75</v>
       </c>
       <c r="D65" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E65" t="s">
         <v>8</v>
       </c>
       <c r="F65" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G65">
         <v>1</v>
@@ -3303,22 +3318,22 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66">
-        <v>23330051920100</v>
+        <v>23330051920354</v>
       </c>
       <c r="B66" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="C66" t="s">
-        <v>137</v>
+        <v>56</v>
       </c>
       <c r="D66" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E66" t="s">
         <v>8</v>
       </c>
       <c r="F66" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G66">
         <v>1</v>
@@ -3326,22 +3341,22 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67">
-        <v>23330051920102</v>
+        <v>23330051920170</v>
       </c>
       <c r="B67" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C67" t="s">
-        <v>42</v>
+        <v>138</v>
       </c>
       <c r="D67" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E67" t="s">
         <v>8</v>
       </c>
       <c r="F67" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G67">
         <v>1</v>
@@ -3349,22 +3364,22 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68">
-        <v>23330051920104</v>
+        <v>23330051920173</v>
       </c>
       <c r="B68" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C68" t="s">
-        <v>138</v>
+        <v>76</v>
       </c>
       <c r="D68" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E68" t="s">
         <v>8</v>
       </c>
       <c r="F68" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G68">
         <v>1</v>
@@ -3372,22 +3387,22 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69">
-        <v>23330051920106</v>
+        <v>23330051920172</v>
       </c>
       <c r="B69" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C69" t="s">
-        <v>139</v>
+        <v>34</v>
       </c>
       <c r="D69" t="s">
-        <v>232</v>
+        <v>199</v>
       </c>
       <c r="E69" t="s">
         <v>8</v>
       </c>
       <c r="F69" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G69">
         <v>1</v>
@@ -3395,13 +3410,13 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70">
-        <v>23330051920108</v>
+        <v>23330051920174</v>
       </c>
       <c r="B70" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C70" t="s">
-        <v>140</v>
+        <v>72</v>
       </c>
       <c r="D70" t="s">
         <v>233</v>
@@ -3410,7 +3425,7 @@
         <v>8</v>
       </c>
       <c r="F70" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G70">
         <v>1</v>
@@ -3418,13 +3433,13 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71">
-        <v>23330051920110</v>
+        <v>23330051920048</v>
       </c>
       <c r="B71" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C71" t="s">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="D71" t="s">
         <v>234</v>
@@ -3433,7 +3448,7 @@
         <v>8</v>
       </c>
       <c r="F71" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G71">
         <v>1</v>
@@ -3441,13 +3456,13 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72">
-        <v>23330051920111</v>
+        <v>23330051920050</v>
       </c>
       <c r="B72" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C72" t="s">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="D72" t="s">
         <v>235</v>
@@ -3456,7 +3471,7 @@
         <v>8</v>
       </c>
       <c r="F72" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G72">
         <v>1</v>
@@ -3464,13 +3479,13 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73">
-        <v>23330051920152</v>
+        <v>23330051920053</v>
       </c>
       <c r="B73" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="C73" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="D73" t="s">
         <v>236</v>
@@ -3479,7 +3494,7 @@
         <v>8</v>
       </c>
       <c r="F73" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G73">
         <v>1</v>
@@ -3487,13 +3502,13 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74">
-        <v>23330051920153</v>
+        <v>23330051920054</v>
       </c>
       <c r="B74" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C74" t="s">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="D74" t="s">
         <v>237</v>
@@ -3502,7 +3517,7 @@
         <v>8</v>
       </c>
       <c r="F74" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G74">
         <v>1</v>
@@ -3510,13 +3525,13 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75">
-        <v>23330051920155</v>
+        <v>23330051920055</v>
       </c>
       <c r="B75" t="s">
-        <v>21</v>
+        <v>76</v>
       </c>
       <c r="C75" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D75" t="s">
         <v>238</v>
@@ -3525,7 +3540,7 @@
         <v>8</v>
       </c>
       <c r="F75" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G75">
         <v>1</v>
@@ -3533,13 +3548,13 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76">
-        <v>23330051920154</v>
+        <v>23330051920056</v>
       </c>
       <c r="B76" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="C76" t="s">
-        <v>142</v>
+        <v>49</v>
       </c>
       <c r="D76" t="s">
         <v>239</v>
@@ -3548,7 +3563,7 @@
         <v>8</v>
       </c>
       <c r="F76" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G76">
         <v>1</v>
@@ -3556,22 +3571,22 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77">
-        <v>23330051920250</v>
+        <v>23330051920057</v>
       </c>
       <c r="B77" t="s">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="C77" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D77" t="s">
-        <v>184</v>
+        <v>240</v>
       </c>
       <c r="E77" t="s">
         <v>8</v>
       </c>
       <c r="F77" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G77">
         <v>1</v>
@@ -3579,22 +3594,22 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78">
-        <v>23330051920157</v>
+        <v>23330051920058</v>
       </c>
       <c r="B78" t="s">
-        <v>27</v>
+        <v>78</v>
       </c>
       <c r="C78" t="s">
-        <v>46</v>
+        <v>111</v>
       </c>
       <c r="D78" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E78" t="s">
         <v>8</v>
       </c>
       <c r="F78" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G78">
         <v>1</v>
@@ -3602,22 +3617,22 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79">
-        <v>23330051920158</v>
+        <v>23330051920060</v>
       </c>
       <c r="B79" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="C79" t="s">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="D79" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E79" t="s">
         <v>8</v>
       </c>
       <c r="F79" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G79">
         <v>1</v>
@@ -3625,22 +3640,22 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80">
-        <v>23330051920159</v>
+        <v>23330051920061</v>
       </c>
       <c r="B80" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="C80" t="s">
-        <v>85</v>
+        <v>141</v>
       </c>
       <c r="D80" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E80" t="s">
         <v>8</v>
       </c>
       <c r="F80" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G80">
         <v>1</v>
@@ -3648,22 +3663,22 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81">
-        <v>23330051920163</v>
+        <v>23330051920307</v>
       </c>
       <c r="B81" t="s">
         <v>80</v>
       </c>
       <c r="C81" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D81" t="s">
-        <v>243</v>
+        <v>221</v>
       </c>
       <c r="E81" t="s">
         <v>8</v>
       </c>
       <c r="F81" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G81">
         <v>1</v>
@@ -3671,13 +3686,13 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82">
-        <v>23330051920297</v>
+        <v>23330051920063</v>
       </c>
       <c r="B82" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C82" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="D82" t="s">
         <v>244</v>
@@ -3686,7 +3701,7 @@
         <v>8</v>
       </c>
       <c r="F82" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G82">
         <v>1</v>
@@ -3694,13 +3709,13 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83">
-        <v>23330051920167</v>
+        <v>23330051920064</v>
       </c>
       <c r="B83" t="s">
-        <v>81</v>
+        <v>38</v>
       </c>
       <c r="C83" t="s">
-        <v>46</v>
+        <v>86</v>
       </c>
       <c r="D83" t="s">
         <v>245</v>
@@ -3709,7 +3724,7 @@
         <v>8</v>
       </c>
       <c r="F83" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G83">
         <v>1</v>
@@ -3717,13 +3732,13 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84">
-        <v>23330051920310</v>
+        <v>23330051920066</v>
       </c>
       <c r="B84" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C84" t="s">
-        <v>28</v>
+        <v>114</v>
       </c>
       <c r="D84" t="s">
         <v>246</v>
@@ -3732,7 +3747,7 @@
         <v>8</v>
       </c>
       <c r="F84" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G84">
         <v>1</v>
@@ -3740,13 +3755,13 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85">
-        <v>23330051920169</v>
+        <v>23330051920067</v>
       </c>
       <c r="B85" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C85" t="s">
-        <v>33</v>
+        <v>143</v>
       </c>
       <c r="D85" t="s">
         <v>247</v>
@@ -3755,7 +3770,7 @@
         <v>8</v>
       </c>
       <c r="F85" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G85">
         <v>1</v>
@@ -3763,13 +3778,13 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86">
-        <v>23330051920354</v>
+        <v>23330051920068</v>
       </c>
       <c r="B86" t="s">
         <v>83</v>
       </c>
       <c r="C86" t="s">
-        <v>71</v>
+        <v>144</v>
       </c>
       <c r="D86" t="s">
         <v>248</v>
@@ -3778,7 +3793,7 @@
         <v>8</v>
       </c>
       <c r="F86" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G86">
         <v>1</v>
@@ -3786,13 +3801,13 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87">
-        <v>23330051920170</v>
+        <v>23330051920069</v>
       </c>
       <c r="B87" t="s">
         <v>84</v>
       </c>
       <c r="C87" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D87" t="s">
         <v>249</v>
@@ -3801,7 +3816,7 @@
         <v>8</v>
       </c>
       <c r="F87" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G87">
         <v>1</v>
@@ -3809,13 +3824,13 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88">
-        <v>23330051920173</v>
+        <v>23330051920070</v>
       </c>
       <c r="B88" t="s">
         <v>85</v>
       </c>
       <c r="C88" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D88" t="s">
         <v>250</v>
@@ -3824,7 +3839,7 @@
         <v>8</v>
       </c>
       <c r="F88" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G88">
         <v>1</v>
@@ -3832,22 +3847,22 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89">
-        <v>23330051920172</v>
+        <v>23330051920272</v>
       </c>
       <c r="B89" t="s">
         <v>86</v>
       </c>
       <c r="C89" t="s">
-        <v>51</v>
+        <v>112</v>
       </c>
       <c r="D89" t="s">
-        <v>217</v>
+        <v>251</v>
       </c>
       <c r="E89" t="s">
         <v>8</v>
       </c>
       <c r="F89" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G89">
         <v>1</v>
@@ -3855,22 +3870,22 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90">
-        <v>23330051920174</v>
+        <v>23330051920074</v>
       </c>
       <c r="B90" t="s">
         <v>87</v>
       </c>
       <c r="C90" t="s">
-        <v>87</v>
+        <v>146</v>
       </c>
       <c r="D90" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E90" t="s">
         <v>8</v>
       </c>
       <c r="F90" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G90">
         <v>1</v>
@@ -3878,22 +3893,22 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91">
-        <v>23330051920031</v>
+        <v>23330051920075</v>
       </c>
       <c r="B91" t="s">
         <v>88</v>
       </c>
       <c r="C91" t="s">
-        <v>145</v>
+        <v>23</v>
       </c>
       <c r="D91" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E91" t="s">
         <v>8</v>
       </c>
       <c r="F91" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G91">
         <v>1</v>
@@ -3901,16 +3916,16 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92">
-        <v>23330051920033</v>
+        <v>23330051920031</v>
       </c>
       <c r="B92" t="s">
         <v>89</v>
       </c>
       <c r="C92" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D92" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E92" t="s">
         <v>8</v>
@@ -3924,16 +3939,16 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93">
-        <v>23330051920034</v>
+        <v>23330051920033</v>
       </c>
       <c r="B93" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="C93" t="s">
-        <v>27</v>
+        <v>148</v>
       </c>
       <c r="D93" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E93" t="s">
         <v>8</v>
@@ -3947,16 +3962,16 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94">
-        <v>23330051920232</v>
+        <v>23330051920034</v>
       </c>
       <c r="B94" t="s">
-        <v>90</v>
+        <v>51</v>
       </c>
       <c r="C94" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D94" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E94" t="s">
         <v>8</v>
@@ -3970,16 +3985,16 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95">
-        <v>23330051920040</v>
+        <v>23330051920232</v>
       </c>
       <c r="B95" t="s">
         <v>91</v>
       </c>
       <c r="C95" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="D95" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E95" t="s">
         <v>8</v>
@@ -3993,16 +4008,16 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96">
-        <v>23330051920041</v>
+        <v>23330051920040</v>
       </c>
       <c r="B96" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="C96" t="s">
-        <v>147</v>
+        <v>95</v>
       </c>
       <c r="D96" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E96" t="s">
         <v>8</v>
@@ -4016,16 +4031,16 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97">
-        <v>23330051920042</v>
+        <v>23330051920041</v>
       </c>
       <c r="B97" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="C97" t="s">
-        <v>21</v>
+        <v>149</v>
       </c>
       <c r="D97" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E97" t="s">
         <v>8</v>
@@ -4039,16 +4054,16 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98">
-        <v>23330051920043</v>
+        <v>23330051920042</v>
       </c>
       <c r="B98" t="s">
-        <v>46</v>
+        <v>93</v>
       </c>
       <c r="C98" t="s">
-        <v>130</v>
+        <v>21</v>
       </c>
       <c r="D98" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E98" t="s">
         <v>8</v>
@@ -4062,16 +4077,16 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99">
-        <v>23330051920044</v>
+        <v>23330051920043</v>
       </c>
       <c r="B99" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C99" t="s">
-        <v>24</v>
+        <v>123</v>
       </c>
       <c r="D99" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E99" t="s">
         <v>8</v>
@@ -4085,16 +4100,16 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100">
-        <v>23330051920209</v>
+        <v>23330051920044</v>
       </c>
       <c r="B100" t="s">
         <v>94</v>
       </c>
       <c r="C100" t="s">
-        <v>148</v>
+        <v>24</v>
       </c>
       <c r="D100" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E100" t="s">
         <v>8</v>
@@ -4108,16 +4123,16 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101">
-        <v>23330051920046</v>
+        <v>23330051920209</v>
       </c>
       <c r="B101" t="s">
         <v>95</v>
       </c>
       <c r="C101" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D101" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E101" t="s">
         <v>8</v>
@@ -4131,22 +4146,22 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102">
-        <v>23330051920117</v>
+        <v>23330051920046</v>
       </c>
       <c r="B102" t="s">
         <v>96</v>
       </c>
       <c r="C102" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D102" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E102" t="s">
         <v>8</v>
       </c>
       <c r="F102" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G102">
         <v>1</v>
@@ -4154,16 +4169,16 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103">
-        <v>23330061460223</v>
+        <v>23330051920117</v>
       </c>
       <c r="B103" t="s">
         <v>97</v>
       </c>
       <c r="C103" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D103" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E103" t="s">
         <v>8</v>
@@ -4177,16 +4192,16 @@
     </row>
     <row r="104" spans="1:7">
       <c r="A104">
-        <v>23330051920119</v>
+        <v>23330061460223</v>
       </c>
       <c r="B104" t="s">
         <v>98</v>
       </c>
       <c r="C104" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D104" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E104" t="s">
         <v>8</v>
@@ -4200,16 +4215,16 @@
     </row>
     <row r="105" spans="1:7">
       <c r="A105">
-        <v>23330051920120</v>
+        <v>23330051920119</v>
       </c>
       <c r="B105" t="s">
         <v>99</v>
       </c>
       <c r="C105" t="s">
-        <v>52</v>
+        <v>154</v>
       </c>
       <c r="D105" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E105" t="s">
         <v>8</v>
@@ -4223,16 +4238,16 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106">
-        <v>23330051920121</v>
+        <v>23330051920120</v>
       </c>
       <c r="B106" t="s">
         <v>100</v>
       </c>
       <c r="C106" t="s">
-        <v>153</v>
+        <v>35</v>
       </c>
       <c r="D106" t="s">
-        <v>175</v>
+        <v>268</v>
       </c>
       <c r="E106" t="s">
         <v>8</v>
@@ -4246,16 +4261,16 @@
     </row>
     <row r="107" spans="1:7">
       <c r="A107">
-        <v>23330051920124</v>
+        <v>23330051920121</v>
       </c>
       <c r="B107" t="s">
-        <v>67</v>
+        <v>101</v>
       </c>
       <c r="C107" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D107" t="s">
-        <v>267</v>
+        <v>235</v>
       </c>
       <c r="E107" t="s">
         <v>8</v>
@@ -4269,16 +4284,16 @@
     </row>
     <row r="108" spans="1:7">
       <c r="A108">
-        <v>23330051920125</v>
+        <v>23330051920124</v>
       </c>
       <c r="B108" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="C108" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D108" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E108" t="s">
         <v>8</v>
@@ -4292,16 +4307,16 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109">
-        <v>23330051920126</v>
+        <v>23330051920125</v>
       </c>
       <c r="B109" t="s">
-        <v>101</v>
+        <v>22</v>
       </c>
       <c r="C109" t="s">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="D109" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E109" t="s">
         <v>8</v>
@@ -4315,16 +4330,16 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110">
-        <v>23330051920127</v>
+        <v>23330051920126</v>
       </c>
       <c r="B110" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="C110" t="s">
-        <v>156</v>
+        <v>70</v>
       </c>
       <c r="D110" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E110" t="s">
         <v>8</v>
@@ -4338,16 +4353,16 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111">
-        <v>23330051920128</v>
+        <v>23330051920127</v>
       </c>
       <c r="B111" t="s">
         <v>27</v>
       </c>
       <c r="C111" t="s">
-        <v>52</v>
+        <v>157</v>
       </c>
       <c r="D111" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E111" t="s">
         <v>8</v>
@@ -4361,16 +4376,16 @@
     </row>
     <row r="112" spans="1:7">
       <c r="A112">
-        <v>23330051920129</v>
+        <v>23330051920128</v>
       </c>
       <c r="B112" t="s">
         <v>27</v>
       </c>
       <c r="C112" t="s">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="D112" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E112" t="s">
         <v>8</v>
@@ -4384,16 +4399,16 @@
     </row>
     <row r="113" spans="1:7">
       <c r="A113">
-        <v>23330051920130</v>
+        <v>23330051920129</v>
       </c>
       <c r="B113" t="s">
         <v>27</v>
       </c>
       <c r="C113" t="s">
-        <v>157</v>
+        <v>56</v>
       </c>
       <c r="D113" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E113" t="s">
         <v>8</v>
@@ -4407,16 +4422,16 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114">
-        <v>23330051920134</v>
+        <v>23330051920130</v>
       </c>
       <c r="B114" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="C114" t="s">
-        <v>27</v>
+        <v>158</v>
       </c>
       <c r="D114" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E114" t="s">
         <v>8</v>
@@ -4430,16 +4445,16 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115">
-        <v>23330051920135</v>
+        <v>23330051920134</v>
       </c>
       <c r="B115" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="C115" t="s">
-        <v>128</v>
+        <v>27</v>
       </c>
       <c r="D115" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E115" t="s">
         <v>8</v>
@@ -4453,16 +4468,16 @@
     </row>
     <row r="116" spans="1:7">
       <c r="A116">
-        <v>23330051920137</v>
+        <v>23330051920135</v>
       </c>
       <c r="B116" t="s">
-        <v>102</v>
+        <v>34</v>
       </c>
       <c r="C116" t="s">
-        <v>158</v>
+        <v>121</v>
       </c>
       <c r="D116" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E116" t="s">
         <v>8</v>
@@ -4476,16 +4491,16 @@
     </row>
     <row r="117" spans="1:7">
       <c r="A117">
-        <v>23330051920140</v>
+        <v>23330051920137</v>
       </c>
       <c r="B117" t="s">
         <v>103</v>
       </c>
       <c r="C117" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="D117" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E117" t="s">
         <v>8</v>
@@ -4499,16 +4514,16 @@
     </row>
     <row r="118" spans="1:7">
       <c r="A118">
-        <v>23330051920138</v>
+        <v>23330051920122</v>
       </c>
       <c r="B118" t="s">
-        <v>104</v>
+        <v>35</v>
       </c>
       <c r="C118" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D118" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E118" t="s">
         <v>8</v>
@@ -4522,16 +4537,16 @@
     </row>
     <row r="119" spans="1:7">
       <c r="A119">
-        <v>23330051920255</v>
+        <v>23330051920140</v>
       </c>
       <c r="B119" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C119" t="s">
-        <v>160</v>
+        <v>115</v>
       </c>
       <c r="D119" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E119" t="s">
         <v>8</v>
@@ -4545,16 +4560,16 @@
     </row>
     <row r="120" spans="1:7">
       <c r="A120">
-        <v>23330051920315</v>
+        <v>23330051920138</v>
       </c>
       <c r="B120" t="s">
-        <v>45</v>
+        <v>105</v>
       </c>
       <c r="C120" t="s">
         <v>161</v>
       </c>
       <c r="D120" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E120" t="s">
         <v>8</v>
@@ -4568,16 +4583,16 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121">
-        <v>23330051920143</v>
+        <v>23330051920255</v>
       </c>
       <c r="B121" t="s">
-        <v>46</v>
+        <v>106</v>
       </c>
       <c r="C121" t="s">
         <v>162</v>
       </c>
       <c r="D121" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E121" t="s">
         <v>8</v>
@@ -4591,16 +4606,16 @@
     </row>
     <row r="122" spans="1:7">
       <c r="A122">
-        <v>23330051920144</v>
+        <v>23330051920315</v>
       </c>
       <c r="B122" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="C122" t="s">
-        <v>60</v>
+        <v>163</v>
       </c>
       <c r="D122" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E122" t="s">
         <v>8</v>
@@ -4614,16 +4629,16 @@
     </row>
     <row r="123" spans="1:7">
       <c r="A123">
-        <v>23330051920146</v>
+        <v>23330051920143</v>
       </c>
       <c r="B123" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C123" t="s">
-        <v>22</v>
+        <v>164</v>
       </c>
       <c r="D123" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E123" t="s">
         <v>8</v>
@@ -4637,16 +4652,16 @@
     </row>
     <row r="124" spans="1:7">
       <c r="A124">
-        <v>23330051920147</v>
+        <v>23330051920144</v>
       </c>
       <c r="B124" t="s">
-        <v>94</v>
+        <v>44</v>
       </c>
       <c r="C124" t="s">
-        <v>163</v>
+        <v>44</v>
       </c>
       <c r="D124" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E124" t="s">
         <v>8</v>
@@ -4660,16 +4675,16 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125">
-        <v>23330051920346</v>
+        <v>23330051920146</v>
       </c>
       <c r="B125" t="s">
-        <v>106</v>
+        <v>70</v>
       </c>
       <c r="C125" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D125" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E125" t="s">
         <v>8</v>
@@ -4683,16 +4698,16 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126">
-        <v>23330051920149</v>
+        <v>23330051920147</v>
       </c>
       <c r="B126" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="C126" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D126" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E126" t="s">
         <v>8</v>
@@ -4701,6 +4716,75 @@
         <v>13</v>
       </c>
       <c r="G126">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7">
+      <c r="A127">
+        <v>23330051920346</v>
+      </c>
+      <c r="B127" t="s">
+        <v>107</v>
+      </c>
+      <c r="C127" t="s">
+        <v>50</v>
+      </c>
+      <c r="D127" t="s">
+        <v>288</v>
+      </c>
+      <c r="E127" t="s">
+        <v>8</v>
+      </c>
+      <c r="F127" t="s">
+        <v>13</v>
+      </c>
+      <c r="G127">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7">
+      <c r="A128">
+        <v>23330051920149</v>
+      </c>
+      <c r="B128" t="s">
+        <v>108</v>
+      </c>
+      <c r="C128" t="s">
+        <v>166</v>
+      </c>
+      <c r="D128" t="s">
+        <v>289</v>
+      </c>
+      <c r="E128" t="s">
+        <v>8</v>
+      </c>
+      <c r="F128" t="s">
+        <v>13</v>
+      </c>
+      <c r="G128">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7">
+      <c r="A129">
+        <v>23330051920150</v>
+      </c>
+      <c r="B129" t="s">
+        <v>109</v>
+      </c>
+      <c r="C129" t="s">
+        <v>25</v>
+      </c>
+      <c r="D129" t="s">
+        <v>290</v>
+      </c>
+      <c r="E129" t="s">
+        <v>8</v>
+      </c>
+      <c r="F129" t="s">
+        <v>13</v>
+      </c>
+      <c r="G129">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20232.xlsx
+++ b/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="356">
   <si>
     <t>Mat</t>
   </si>
@@ -82,264 +82,327 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LARRACILLA</t>
+  </si>
+  <si>
+    <t>VIVANCO</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>LOBATO</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>AMARO</t>
+  </si>
+  <si>
+    <t>BAROJAS</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>TAPIA</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>BUSTOS</t>
+  </si>
+  <si>
+    <t>CERONIO</t>
+  </si>
+  <si>
+    <t>CHICO</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>LARA</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
+    <t>NARVAEZ</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
+    <t>ALTAMIRA</t>
+  </si>
+  <si>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
+    <t>AZPIRI</t>
+  </si>
+  <si>
+    <t>BONOLA</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>ESCOBEDO</t>
+  </si>
+  <si>
+    <t>FUENTES</t>
   </si>
   <si>
     <t>GUERRA</t>
   </si>
   <si>
-    <t>PEREZ</t>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>PASTRANA</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
   </si>
   <si>
     <t>SANTOS</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
+    <t>SEGURA</t>
+  </si>
+  <si>
+    <t>SILVESTRE</t>
+  </si>
+  <si>
+    <t>YOPIHUA</t>
+  </si>
+  <si>
+    <t>ABREGO</t>
+  </si>
+  <si>
+    <t>ANGEL</t>
+  </si>
+  <si>
+    <t>BONILLA</t>
   </si>
   <si>
     <t>HERRERA</t>
   </si>
   <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MELO</t>
+  </si>
+  <si>
     <t>MOLINA</t>
   </si>
   <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>RIOS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>ANDRES</t>
+  </si>
+  <si>
+    <t>ARENAS</t>
+  </si>
+  <si>
+    <t>BACILIO</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>COXCAHUA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
+    <t>GUERRERO</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
     <t>HUERTA</t>
   </si>
   <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
+    <t>MATA</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>PIMENTEL</t>
+  </si>
+  <si>
+    <t>QUIROGA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>SOSA</t>
+  </si>
+  <si>
+    <t>XALAMIHUA</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
   </si>
   <si>
     <t>CORDOVA</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
+    <t>ECHAVARRIA</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
   </si>
   <si>
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
+    <t>MEJIA</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>OROZCO</t>
+  </si>
+  <si>
+    <t>SAAVEDRA</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>ARRIETA</t>
+  </si>
+  <si>
+    <t>BORBONIO</t>
+  </si>
+  <si>
+    <t>CARRASCO</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>GIL</t>
+  </si>
+  <si>
+    <t>IXTLA</t>
+  </si>
+  <si>
+    <t>MAY</t>
+  </si>
+  <si>
+    <t>MARIN</t>
+  </si>
+  <si>
+    <t>MORENO</t>
   </si>
   <si>
     <t>RUGERIO</t>
   </si>
   <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>BUSTOS</t>
-  </si>
-  <si>
-    <t>CERONIO</t>
-  </si>
-  <si>
-    <t>LARA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>ALTAMIRA</t>
-  </si>
-  <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>ESCOBEDO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>FUENTES</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>PASTRANA</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>SILVESTRE</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>ANGEL</t>
-  </si>
-  <si>
-    <t>BONILLA</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>RIOS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>BACILIO</t>
-  </si>
-  <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
-    <t>GUERRERO</t>
-  </si>
-  <si>
-    <t>MATA</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>PIMENTEL</t>
-  </si>
-  <si>
-    <t>QUIROGA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>SOSA</t>
-  </si>
-  <si>
-    <t>XALAMIHUA</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>ECHAVARRIA</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>OROZCO</t>
-  </si>
-  <si>
-    <t>SAAVEDRA</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>ARRIETA</t>
-  </si>
-  <si>
-    <t>BORBONIO</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>GIL</t>
-  </si>
-  <si>
-    <t>IXTLA</t>
-  </si>
-  <si>
-    <t>MAY</t>
-  </si>
-  <si>
-    <t>MARIN</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
     <t>TLAXCALA</t>
   </si>
   <si>
@@ -349,217 +412,562 @@
     <t>XOTLANIHUA</t>
   </si>
   <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>CRISTOBAL</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
+  </si>
+  <si>
+    <t>VANEGAS</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>DAMIAN</t>
+  </si>
+  <si>
+    <t>MIXCOA</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>LAGUNA</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>VARILLAS</t>
+  </si>
+  <si>
+    <t>CAMARILLO</t>
+  </si>
+  <si>
+    <t>NUBE</t>
+  </si>
+  <si>
+    <t>CARPINTEYRO</t>
+  </si>
+  <si>
+    <t>TZANAHUA</t>
   </si>
   <si>
     <t>ARIAS</t>
   </si>
   <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>ALDUCIN</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>TELLEZ</t>
+  </si>
+  <si>
+    <t>MIXTECO</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>TOLENTINO</t>
+  </si>
+  <si>
+    <t>NIEVES</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
     <t>TETLA</t>
   </si>
   <si>
     <t>AMADOR</t>
   </si>
   <si>
+    <t>TENCHIPE</t>
+  </si>
+  <si>
+    <t>CORREA</t>
+  </si>
+  <si>
+    <t>CALCANEO</t>
+  </si>
+  <si>
+    <t>ATILANO</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>POOT</t>
+  </si>
+  <si>
+    <t>CANSECO</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>ENRIQUEZ</t>
+  </si>
+  <si>
+    <t>CAMACHO</t>
+  </si>
+  <si>
+    <t>FIGUEROA</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
     <t>TORRES</t>
   </si>
   <si>
+    <t>DURAND</t>
+  </si>
+  <si>
     <t>MARCELINO</t>
   </si>
   <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>VOTE</t>
+    <t>PANZO</t>
+  </si>
+  <si>
+    <t>URBINA</t>
+  </si>
+  <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
+    <t>NAVA</t>
+  </si>
+  <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>MONTERROSA</t>
+  </si>
+  <si>
+    <t>HILARIO</t>
+  </si>
+  <si>
+    <t>ZOPIYACTLE</t>
+  </si>
+  <si>
+    <t>DECTOR</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>VIDAL</t>
+  </si>
+  <si>
+    <t>ARCOS</t>
   </si>
   <si>
     <t>BAUTISTA</t>
   </si>
   <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>VARILLAS</t>
-  </si>
-  <si>
-    <t>CARPINTEYRO</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>ALDUCIN</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>TELLEZ</t>
-  </si>
-  <si>
-    <t>TOLENTINO</t>
-  </si>
-  <si>
-    <t>NIEVES</t>
-  </si>
-  <si>
-    <t>TENCHIPE</t>
-  </si>
-  <si>
-    <t>CORREA</t>
-  </si>
-  <si>
-    <t>ATILANO</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>POOT</t>
-  </si>
-  <si>
-    <t>CANSECO</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>ENRIQUEZ</t>
-  </si>
-  <si>
-    <t>CAMACHO</t>
-  </si>
-  <si>
-    <t>FIGUEROA</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>DURAND</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>URBINA</t>
-  </si>
-  <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
-    <t>NAVA</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>MONTERROSA</t>
-  </si>
-  <si>
-    <t>HILARIO</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>ZOPIYACTLE</t>
-  </si>
-  <si>
-    <t>DECTOR</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>VIDAL</t>
-  </si>
-  <si>
-    <t>ARCOS</t>
-  </si>
-  <si>
     <t>MANZANO</t>
   </si>
   <si>
-    <t>MIXCOA</t>
-  </si>
-  <si>
     <t>TELE</t>
   </si>
   <si>
     <t>SALINAS</t>
   </si>
   <si>
+    <t>KEVYN DANIEL</t>
+  </si>
+  <si>
+    <t>SABDY</t>
+  </si>
+  <si>
+    <t>TRISTAN YABAL</t>
+  </si>
+  <si>
+    <t>LUIS FABIAN</t>
+  </si>
+  <si>
+    <t>SERGIO JOSUE</t>
+  </si>
+  <si>
+    <t>DIEGO ARMANDO</t>
+  </si>
+  <si>
+    <t>ANGEL CHARBEL</t>
+  </si>
+  <si>
+    <t>YAMILET</t>
+  </si>
+  <si>
+    <t>ARIATNA</t>
+  </si>
+  <si>
+    <t>MELANY</t>
+  </si>
+  <si>
+    <t>MARGARITA</t>
+  </si>
+  <si>
+    <t>MONICA</t>
+  </si>
+  <si>
+    <t>LUIS AARON</t>
+  </si>
+  <si>
+    <t>JESUS JAREF</t>
+  </si>
+  <si>
+    <t>IRVING</t>
+  </si>
+  <si>
+    <t>ANA KAREN</t>
+  </si>
+  <si>
+    <t>JAZIEL</t>
+  </si>
+  <si>
+    <t>ALEX URIEL</t>
+  </si>
+  <si>
+    <t>ISAAC</t>
+  </si>
+  <si>
+    <t>ANGEL DANIEL</t>
+  </si>
+  <si>
+    <t>AXEL</t>
+  </si>
+  <si>
+    <t>ABRIL AMAYRANI</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>JOSE EMILIANO</t>
+  </si>
+  <si>
+    <t>JOSE ALDAIR</t>
+  </si>
+  <si>
+    <t>FERNANDO</t>
+  </si>
+  <si>
     <t>EMMANUEL</t>
   </si>
   <si>
-    <t>KEVYN DANIEL</t>
-  </si>
-  <si>
-    <t>ANGEL CHARBEL</t>
+    <t>JOSE ANTONIO</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>JUAN RAMON</t>
+  </si>
+  <si>
+    <t>LAZARO</t>
+  </si>
+  <si>
+    <t>ROBBIE ALONSO</t>
+  </si>
+  <si>
+    <t>ANTHONY</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>LINET</t>
+  </si>
+  <si>
+    <t>SAUL</t>
+  </si>
+  <si>
+    <t>XIMENA</t>
+  </si>
+  <si>
+    <t>ANGEL NAIN</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>MARIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>OSWALDO</t>
+  </si>
+  <si>
+    <t>JANETH</t>
+  </si>
+  <si>
+    <t>ILSE JIMENA</t>
+  </si>
+  <si>
+    <t>DAYANA ASTRID</t>
+  </si>
+  <si>
+    <t>MARIAM MICHAELL</t>
+  </si>
+  <si>
+    <t>LAURA ISABEL</t>
+  </si>
+  <si>
+    <t>VIRIDIANA</t>
   </si>
   <si>
     <t>ALEX TADEO</t>
   </si>
   <si>
+    <t>YEIMI ALEXANDER</t>
+  </si>
+  <si>
+    <t>DIEGO GREGORIO</t>
+  </si>
+  <si>
+    <t>ANGEL EDUC</t>
+  </si>
+  <si>
+    <t>AXEL JOSUE</t>
+  </si>
+  <si>
+    <t>ANGELA</t>
+  </si>
+  <si>
+    <t>REY</t>
+  </si>
+  <si>
     <t>ARELI DANAE</t>
   </si>
   <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>ANIELA SAMANTA</t>
+  </si>
+  <si>
+    <t>CONCEPCION GUADALUPE</t>
+  </si>
+  <si>
     <t>MIRANDA</t>
   </si>
   <si>
+    <t>DAFNE</t>
+  </si>
+  <si>
+    <t>HEIDI</t>
+  </si>
+  <si>
+    <t>ARIADNA JARETZI</t>
+  </si>
+  <si>
+    <t>ALDO</t>
+  </si>
+  <si>
+    <t>GUADALUPE ANAHI</t>
+  </si>
+  <si>
+    <t>SULU ALAN</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>ESTRELLA ESMERALDA</t>
+  </si>
+  <si>
+    <t>ESTRELLA RUBI</t>
+  </si>
+  <si>
+    <t>XOCHITL ALELI</t>
+  </si>
+  <si>
+    <t>ANDREA</t>
+  </si>
+  <si>
+    <t>JAIR</t>
+  </si>
+  <si>
+    <t>DORIAN ALEXANDER</t>
+  </si>
+  <si>
+    <t>JUAN PABLO</t>
+  </si>
+  <si>
     <t>HECTOR</t>
   </si>
   <si>
     <t>JOSELYN</t>
   </si>
   <si>
+    <t>KEIRA</t>
+  </si>
+  <si>
+    <t>URIEL</t>
+  </si>
+  <si>
+    <t>KENYA MARIANA</t>
+  </si>
+  <si>
     <t>LEONARDO GABRIEL</t>
   </si>
   <si>
-    <t>MARIA FERNANDA</t>
+    <t>SALMA JANET</t>
+  </si>
+  <si>
+    <t>JESHUA</t>
+  </si>
+  <si>
+    <t>VICTOR JESUS</t>
+  </si>
+  <si>
+    <t>ELIUD EDUARDO</t>
+  </si>
+  <si>
+    <t>KAORY AYELEN</t>
+  </si>
+  <si>
+    <t>MARIEL</t>
+  </si>
+  <si>
+    <t>JUAN CARLOS</t>
+  </si>
+  <si>
+    <t>DAVID</t>
+  </si>
+  <si>
+    <t>YAELIS</t>
+  </si>
+  <si>
+    <t>PAOLA</t>
+  </si>
+  <si>
+    <t>MARIA GUADALUPE</t>
+  </si>
+  <si>
+    <t>ARIADNA</t>
+  </si>
+  <si>
+    <t>MAR EDITH</t>
+  </si>
+  <si>
+    <t>MELISA</t>
+  </si>
+  <si>
+    <t>JUAN ALONSO</t>
+  </si>
+  <si>
+    <t>CRIZULY AMITHAI</t>
+  </si>
+  <si>
+    <t>ADIEL ALONSO</t>
+  </si>
+  <si>
+    <t>LLUVIA ITZEL</t>
+  </si>
+  <si>
+    <t>EUNICE</t>
+  </si>
+  <si>
+    <t>REYNA IVETT</t>
+  </si>
+  <si>
+    <t>HANNA MONTSERRAT</t>
+  </si>
+  <si>
+    <t>KAROL BALAAM</t>
+  </si>
+  <si>
+    <t>MELANIE YARETZI</t>
   </si>
   <si>
     <t>DENISSE</t>
   </si>
   <si>
+    <t>ANGEL GABRIEL</t>
+  </si>
+  <si>
+    <t>YASMIN</t>
+  </si>
+  <si>
+    <t>XIMENA ANALY</t>
+  </si>
+  <si>
+    <t>ROSA EVELYN</t>
+  </si>
+  <si>
+    <t>VANIA</t>
+  </si>
+  <si>
+    <t>DARLA AMERICA</t>
+  </si>
+  <si>
+    <t>SAMANTHA BETHANY</t>
+  </si>
+  <si>
+    <t>IVONNE ERIMAR</t>
+  </si>
+  <si>
+    <t>MARIEL BIDEMI</t>
+  </si>
+  <si>
+    <t>CARMEN VANELI</t>
+  </si>
+  <si>
     <t>NAIDELYN</t>
   </si>
   <si>
+    <t>ELIAS IGNACIO</t>
+  </si>
+  <si>
     <t>JOSE GUADALUPE</t>
   </si>
   <si>
-    <t>ANA KAREN</t>
+    <t>KEVIN SANTIAGO</t>
+  </si>
+  <si>
+    <t>JOSE EMMANUEL</t>
   </si>
   <si>
     <t>JOSE LUIS</t>
@@ -571,310 +979,97 @@
     <t>EDUARDO</t>
   </si>
   <si>
-    <t>CAMILO</t>
+    <t>JOSE FRANCISCO</t>
+  </si>
+  <si>
+    <t>ALAN URIEL</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>JOANNA OCTAVIA</t>
+  </si>
+  <si>
+    <t>IAN</t>
+  </si>
+  <si>
+    <t>JOSE ARTURO</t>
+  </si>
+  <si>
+    <t>ARELY SUSANA</t>
+  </si>
+  <si>
+    <t>YAEL ISSAI</t>
+  </si>
+  <si>
+    <t>IRMA GUADALUPE</t>
+  </si>
+  <si>
+    <t>BRENDA</t>
+  </si>
+  <si>
+    <t>HELI AIMEE</t>
+  </si>
+  <si>
+    <t>AYLIN AMADA</t>
+  </si>
+  <si>
+    <t>JULIAN DAVID</t>
+  </si>
+  <si>
+    <t>CARLOS OCTAVIO</t>
+  </si>
+  <si>
+    <t>ANGELICA</t>
+  </si>
+  <si>
+    <t>ERNESTO</t>
+  </si>
+  <si>
+    <t>SINAI</t>
+  </si>
+  <si>
+    <t>ARANTZA NAHOMI</t>
+  </si>
+  <si>
+    <t>TATIANA</t>
   </si>
   <si>
     <t>DANIA LIZETH</t>
   </si>
   <si>
+    <t>KENIA PAOLA</t>
+  </si>
+  <si>
+    <t>DIANA</t>
+  </si>
+  <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
     <t>MARITZA</t>
   </si>
   <si>
+    <t>MIRIAM NEFTALI</t>
+  </si>
+  <si>
+    <t>CINTHIA</t>
+  </si>
+  <si>
     <t>MARYGELLI</t>
   </si>
   <si>
+    <t>ANGEL URIEL</t>
+  </si>
+  <si>
+    <t>MICHELLE</t>
+  </si>
+  <si>
     <t>MAGALY</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>JOSE EMILIANO</t>
-  </si>
-  <si>
-    <t>JOSE ALDAIR</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>ROBBIE ALONSO</t>
-  </si>
-  <si>
-    <t>ANTHONY</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>ISAAC</t>
-  </si>
-  <si>
-    <t>LINET</t>
-  </si>
-  <si>
-    <t>SAUL</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>OSWALDO</t>
-  </si>
-  <si>
-    <t>JANETH</t>
-  </si>
-  <si>
-    <t>ILSE JIMENA</t>
-  </si>
-  <si>
-    <t>DAYANA ASTRID</t>
-  </si>
-  <si>
-    <t>MARIAM MICHAELL</t>
-  </si>
-  <si>
-    <t>LAURA ISABEL</t>
-  </si>
-  <si>
-    <t>VIRIDIANA</t>
-  </si>
-  <si>
-    <t>YEIMI ALEXANDER</t>
-  </si>
-  <si>
-    <t>DIEGO GREGORIO</t>
-  </si>
-  <si>
-    <t>ANGEL EDUC</t>
-  </si>
-  <si>
-    <t>AXEL JOSUE</t>
-  </si>
-  <si>
-    <t>ANGELA</t>
-  </si>
-  <si>
-    <t>REY</t>
-  </si>
-  <si>
-    <t>CONCEPCION GUADALUPE</t>
-  </si>
-  <si>
-    <t>DAFNE</t>
-  </si>
-  <si>
-    <t>HEIDI</t>
-  </si>
-  <si>
-    <t>ARIADNA JARETZI</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>ESTRELLA ESMERALDA</t>
-  </si>
-  <si>
-    <t>ESTRELLA RUBI</t>
-  </si>
-  <si>
-    <t>ANDREA</t>
-  </si>
-  <si>
-    <t>JAIR</t>
-  </si>
-  <si>
-    <t>DORIAN ALEXANDER</t>
-  </si>
-  <si>
-    <t>JUAN PABLO</t>
-  </si>
-  <si>
-    <t>KEIRA</t>
-  </si>
-  <si>
-    <t>URIEL</t>
-  </si>
-  <si>
-    <t>SALMA JANET</t>
-  </si>
-  <si>
-    <t>JESHUA</t>
-  </si>
-  <si>
-    <t>VICTOR JESUS</t>
-  </si>
-  <si>
-    <t>ELIUD EDUARDO</t>
-  </si>
-  <si>
-    <t>KAORY AYELEN</t>
-  </si>
-  <si>
-    <t>MARIEL</t>
-  </si>
-  <si>
-    <t>JUAN CARLOS</t>
-  </si>
-  <si>
-    <t>DAVID</t>
-  </si>
-  <si>
-    <t>PAOLA</t>
-  </si>
-  <si>
-    <t>ARIADNA</t>
-  </si>
-  <si>
-    <t>MAR EDITH</t>
-  </si>
-  <si>
-    <t>MELISA</t>
-  </si>
-  <si>
-    <t>JUAN ALONSO</t>
-  </si>
-  <si>
-    <t>CRIZULY AMITHAI</t>
-  </si>
-  <si>
-    <t>ADIEL ALONSO</t>
-  </si>
-  <si>
-    <t>EUNICE</t>
-  </si>
-  <si>
-    <t>REYNA IVETT</t>
-  </si>
-  <si>
-    <t>HANNA MONTSERRAT</t>
-  </si>
-  <si>
-    <t>KAROL BALAAM</t>
-  </si>
-  <si>
-    <t>YASMIN</t>
-  </si>
-  <si>
-    <t>XIMENA ANALY</t>
-  </si>
-  <si>
-    <t>ROSA EVELYN</t>
-  </si>
-  <si>
-    <t>VANIA</t>
-  </si>
-  <si>
-    <t>DARLA AMERICA</t>
-  </si>
-  <si>
-    <t>SAMANTHA BETHANY</t>
-  </si>
-  <si>
-    <t>MARIEL BIDEMI</t>
-  </si>
-  <si>
-    <t>CARMEN VANELI</t>
-  </si>
-  <si>
-    <t>ELIAS IGNACIO</t>
-  </si>
-  <si>
-    <t>KEVIN SANTIAGO</t>
-  </si>
-  <si>
-    <t>JOSE EMMANUEL</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>ALAN URIEL</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>JOANNA OCTAVIA</t>
-  </si>
-  <si>
-    <t>IAN</t>
-  </si>
-  <si>
-    <t>JOSE ARTURO</t>
-  </si>
-  <si>
-    <t>ARELY SUSANA</t>
-  </si>
-  <si>
-    <t>YAEL ISSAI</t>
-  </si>
-  <si>
-    <t>IRMA GUADALUPE</t>
-  </si>
-  <si>
-    <t>BRENDA</t>
-  </si>
-  <si>
-    <t>HELI AIMEE</t>
-  </si>
-  <si>
-    <t>AYLIN AMADA</t>
-  </si>
-  <si>
-    <t>JULIAN DAVID</t>
-  </si>
-  <si>
-    <t>CARLOS OCTAVIO</t>
-  </si>
-  <si>
-    <t>ANGELICA</t>
-  </si>
-  <si>
-    <t>ERNESTO</t>
-  </si>
-  <si>
-    <t>SINAI</t>
-  </si>
-  <si>
-    <t>ARANTZA NAHOMI</t>
-  </si>
-  <si>
-    <t>TATIANA</t>
-  </si>
-  <si>
-    <t>KENIA PAOLA</t>
-  </si>
-  <si>
-    <t>DIANA</t>
-  </si>
-  <si>
-    <t>MELANY</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MIRIAM NEFTALI</t>
-  </si>
-  <si>
-    <t>CINTHIA</t>
-  </si>
-  <si>
-    <t>ANGEL URIEL</t>
-  </si>
-  <si>
-    <t>MICHELLE</t>
-  </si>
-  <si>
-    <t>AXEL</t>
   </si>
   <si>
     <t>LEYLA SARAI</t>
@@ -1814,7 +2009,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G129"/>
+  <dimension ref="A1:G167"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1846,16 +2041,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920185</v>
+        <v>23330051920192</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>110</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>167</v>
+        <v>199</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1869,16 +2064,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920192</v>
+        <v>23330051920329</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>131</v>
       </c>
       <c r="D3" t="s">
-        <v>168</v>
+        <v>200</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1892,16 +2087,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920050</v>
+        <v>22330051920196</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="D4" t="s">
-        <v>169</v>
+        <v>201</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1915,22 +2110,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920234</v>
+        <v>23330051920203</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D5" t="s">
-        <v>170</v>
+        <v>202</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1938,22 +2133,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920103</v>
+        <v>23330051920332</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>133</v>
       </c>
       <c r="D6" t="s">
-        <v>171</v>
+        <v>203</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1961,22 +2156,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920107</v>
+        <v>23330051920211</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>134</v>
       </c>
       <c r="D7" t="s">
-        <v>172</v>
+        <v>204</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1984,22 +2179,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920160</v>
+        <v>22330051920050</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>113</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>173</v>
+        <v>205</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -2007,22 +2202,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920161</v>
+        <v>23330051920090</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>114</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -2030,22 +2225,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920166</v>
+        <v>23330051920101</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>135</v>
       </c>
       <c r="D10" t="s">
-        <v>175</v>
+        <v>207</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -2053,22 +2248,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920062</v>
+        <v>23330051920105</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>52</v>
+        <v>98</v>
       </c>
       <c r="D11" t="s">
-        <v>176</v>
+        <v>208</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -2076,22 +2271,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920065</v>
+        <v>23330051920112</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="D12" t="s">
-        <v>177</v>
+        <v>209</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -2099,22 +2294,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920029</v>
+        <v>23330051920342</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D13" t="s">
-        <v>178</v>
+        <v>206</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -2122,22 +2317,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920030</v>
+        <v>23330051920164</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D14" t="s">
-        <v>179</v>
+        <v>210</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -2145,22 +2340,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920007</v>
+        <v>23330051920313</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D15" t="s">
-        <v>180</v>
+        <v>211</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G15">
         <v>2</v>
@@ -2168,16 +2363,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920035</v>
+        <v>23330051920181</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>137</v>
       </c>
       <c r="D16" t="s">
-        <v>181</v>
+        <v>212</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -2191,16 +2386,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920037</v>
+        <v>23330051920028</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>117</v>
+        <v>30</v>
       </c>
       <c r="D17" t="s">
-        <v>182</v>
+        <v>213</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -2214,16 +2409,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920032</v>
+        <v>22330051920007</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>118</v>
+        <v>21</v>
       </c>
       <c r="D18" t="s">
-        <v>183</v>
+        <v>214</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -2237,22 +2432,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330061460232</v>
+        <v>23330051920039</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="D19" t="s">
-        <v>184</v>
+        <v>215</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G19">
         <v>2</v>
@@ -2260,22 +2455,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>23330051920133</v>
+        <v>23330051920212</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="D20" t="s">
-        <v>185</v>
+        <v>216</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G20">
         <v>2</v>
@@ -2283,16 +2478,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>23330051920139</v>
+        <v>23330051920116</v>
       </c>
       <c r="B21" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C21" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="D21" t="s">
-        <v>186</v>
+        <v>217</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -2306,16 +2501,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>23330051920141</v>
+        <v>23330051920118</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="C22" t="s">
-        <v>120</v>
+        <v>25</v>
       </c>
       <c r="D22" t="s">
-        <v>187</v>
+        <v>218</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -2329,16 +2524,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>23330051920145</v>
+        <v>23330051920144</v>
       </c>
       <c r="B23" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C23" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="D23" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -2352,39 +2547,39 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>23330051920179</v>
+        <v>23330051920148</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C24" t="s">
-        <v>121</v>
+        <v>21</v>
       </c>
       <c r="D24" t="s">
-        <v>189</v>
+        <v>220</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G24">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>23330051920180</v>
+        <v>23330051920179</v>
       </c>
       <c r="B25" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C25" t="s">
-        <v>34</v>
+        <v>140</v>
       </c>
       <c r="D25" t="s">
-        <v>190</v>
+        <v>221</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -2398,16 +2593,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>23330051920182</v>
+        <v>23330051920180</v>
       </c>
       <c r="B26" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C26" t="s">
-        <v>122</v>
+        <v>32</v>
       </c>
       <c r="D26" t="s">
-        <v>191</v>
+        <v>222</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -2421,16 +2616,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>23330051920199</v>
+        <v>23330051920182</v>
       </c>
       <c r="B27" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C27" t="s">
-        <v>55</v>
+        <v>141</v>
       </c>
       <c r="D27" t="s">
-        <v>192</v>
+        <v>223</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -2444,16 +2639,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>23330051920204</v>
+        <v>23330051920183</v>
       </c>
       <c r="B28" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="C28" t="s">
-        <v>123</v>
+        <v>30</v>
       </c>
       <c r="D28" t="s">
-        <v>193</v>
+        <v>224</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -2467,16 +2662,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>23330051920206</v>
+        <v>23330051920185</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C29" t="s">
-        <v>124</v>
+        <v>89</v>
       </c>
       <c r="D29" t="s">
-        <v>194</v>
+        <v>225</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -2490,16 +2685,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>23330051920186</v>
+        <v>22330051920389</v>
       </c>
       <c r="B30" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C30" t="s">
-        <v>23</v>
+        <v>142</v>
       </c>
       <c r="D30" t="s">
-        <v>195</v>
+        <v>226</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -2513,16 +2708,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>23330051920210</v>
+        <v>23330051920199</v>
       </c>
       <c r="B31" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C31" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="D31" t="s">
-        <v>196</v>
+        <v>227</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -2536,22 +2731,22 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>23330051920078</v>
+        <v>23330051920201</v>
       </c>
       <c r="B32" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C32" t="s">
-        <v>27</v>
+        <v>110</v>
       </c>
       <c r="D32" t="s">
-        <v>197</v>
+        <v>228</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
       </c>
       <c r="F32" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -2559,22 +2754,22 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>23330051920077</v>
+        <v>23330051920202</v>
       </c>
       <c r="B33" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C33" t="s">
-        <v>125</v>
+        <v>24</v>
       </c>
       <c r="D33" t="s">
-        <v>198</v>
+        <v>229</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
       </c>
       <c r="F33" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -2582,22 +2777,22 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>23330051920082</v>
+        <v>23330051920204</v>
       </c>
       <c r="B34" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="C34" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="D34" t="s">
-        <v>199</v>
+        <v>230</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
       </c>
       <c r="F34" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -2605,22 +2800,22 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>23330051920085</v>
+        <v>23330051920206</v>
       </c>
       <c r="B35" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="C35" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="D35" t="s">
-        <v>200</v>
+        <v>231</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
       </c>
       <c r="F35" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -2628,22 +2823,22 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>23330051920086</v>
+        <v>23330051920186</v>
       </c>
       <c r="B36" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="C36" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="D36" t="s">
-        <v>201</v>
+        <v>232</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
       </c>
       <c r="F36" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G36">
         <v>1</v>
@@ -2651,22 +2846,22 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>23330051920084</v>
+        <v>23330051920210</v>
       </c>
       <c r="B37" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C37" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="D37" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
       </c>
       <c r="F37" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -2674,16 +2869,16 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>23330051920087</v>
+        <v>23330051920078</v>
       </c>
       <c r="B38" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C38" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D38" t="s">
-        <v>203</v>
+        <v>233</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
@@ -2697,16 +2892,16 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>23330051920088</v>
+        <v>23330051920077</v>
       </c>
       <c r="B39" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C39" t="s">
-        <v>25</v>
+        <v>144</v>
       </c>
       <c r="D39" t="s">
-        <v>204</v>
+        <v>234</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
@@ -2720,16 +2915,16 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>23330051920089</v>
+        <v>23330051920079</v>
       </c>
       <c r="B40" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C40" t="s">
-        <v>78</v>
+        <v>145</v>
       </c>
       <c r="D40" t="s">
-        <v>205</v>
+        <v>235</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
@@ -2743,16 +2938,16 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>23330051920091</v>
+        <v>23330051920080</v>
       </c>
       <c r="B41" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="C41" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="D41" t="s">
-        <v>206</v>
+        <v>236</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
@@ -2766,16 +2961,16 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>23330051920094</v>
+        <v>23330051920082</v>
       </c>
       <c r="B42" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C42" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="D42" t="s">
-        <v>207</v>
+        <v>237</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
@@ -2789,16 +2984,16 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>23330051920251</v>
+        <v>23330051920081</v>
       </c>
       <c r="B43" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="C43" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="D43" t="s">
-        <v>208</v>
+        <v>238</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
@@ -2812,16 +3007,16 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>23330051920099</v>
+        <v>23330051920085</v>
       </c>
       <c r="B44" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C44" t="s">
-        <v>129</v>
+        <v>35</v>
       </c>
       <c r="D44" t="s">
-        <v>209</v>
+        <v>239</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
@@ -2835,16 +3030,16 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>23330051920098</v>
+        <v>23330051920086</v>
       </c>
       <c r="B45" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C45" t="s">
-        <v>130</v>
+        <v>53</v>
       </c>
       <c r="D45" t="s">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
@@ -2858,16 +3053,16 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>23330051920100</v>
+        <v>23330051920084</v>
       </c>
       <c r="B46" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="C46" t="s">
-        <v>131</v>
+        <v>28</v>
       </c>
       <c r="D46" t="s">
-        <v>211</v>
+        <v>241</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
@@ -2881,16 +3076,16 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
-        <v>23330051920102</v>
+        <v>23330051920087</v>
       </c>
       <c r="B47" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C47" t="s">
-        <v>82</v>
+        <v>21</v>
       </c>
       <c r="D47" t="s">
-        <v>212</v>
+        <v>242</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
@@ -2904,16 +3099,16 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48">
-        <v>23330051920104</v>
+        <v>23330051920088</v>
       </c>
       <c r="B48" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="C48" t="s">
-        <v>132</v>
+        <v>24</v>
       </c>
       <c r="D48" t="s">
-        <v>176</v>
+        <v>243</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
@@ -2927,16 +3122,16 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49">
-        <v>23330051920106</v>
+        <v>23330051920089</v>
       </c>
       <c r="B49" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C49" t="s">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="D49" t="s">
-        <v>213</v>
+        <v>244</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
@@ -2950,16 +3145,16 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50">
-        <v>23330051920108</v>
+        <v>23330051920091</v>
       </c>
       <c r="B50" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="C50" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="D50" t="s">
-        <v>214</v>
+        <v>245</v>
       </c>
       <c r="E50" t="s">
         <v>8</v>
@@ -2973,16 +3168,16 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51">
-        <v>23330051920110</v>
+        <v>23330051920234</v>
       </c>
       <c r="B51" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C51" t="s">
-        <v>70</v>
+        <v>149</v>
       </c>
       <c r="D51" t="s">
-        <v>215</v>
+        <v>246</v>
       </c>
       <c r="E51" t="s">
         <v>8</v>
@@ -2996,16 +3191,16 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52">
-        <v>23330051920111</v>
+        <v>23330051920094</v>
       </c>
       <c r="B52" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="C52" t="s">
-        <v>21</v>
+        <v>150</v>
       </c>
       <c r="D52" t="s">
-        <v>216</v>
+        <v>247</v>
       </c>
       <c r="E52" t="s">
         <v>8</v>
@@ -3019,22 +3214,22 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53">
-        <v>23330051920152</v>
+        <v>23330051920251</v>
       </c>
       <c r="B53" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C53" t="s">
-        <v>135</v>
+        <v>28</v>
       </c>
       <c r="D53" t="s">
-        <v>217</v>
+        <v>248</v>
       </c>
       <c r="E53" t="s">
         <v>8</v>
       </c>
       <c r="F53" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G53">
         <v>1</v>
@@ -3042,22 +3237,22 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54">
-        <v>23330051920153</v>
+        <v>23330051920099</v>
       </c>
       <c r="B54" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C54" t="s">
-        <v>62</v>
+        <v>151</v>
       </c>
       <c r="D54" t="s">
-        <v>218</v>
+        <v>249</v>
       </c>
       <c r="E54" t="s">
         <v>8</v>
       </c>
       <c r="F54" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G54">
         <v>1</v>
@@ -3065,22 +3260,22 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55">
-        <v>23330051920155</v>
+        <v>23330051920098</v>
       </c>
       <c r="B55" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="C55" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="D55" t="s">
-        <v>219</v>
+        <v>250</v>
       </c>
       <c r="E55" t="s">
         <v>8</v>
       </c>
       <c r="F55" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G55">
         <v>1</v>
@@ -3088,22 +3283,22 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56">
-        <v>23330051920154</v>
+        <v>23330051920100</v>
       </c>
       <c r="B56" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C56" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="D56" t="s">
-        <v>220</v>
+        <v>251</v>
       </c>
       <c r="E56" t="s">
         <v>8</v>
       </c>
       <c r="F56" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G56">
         <v>1</v>
@@ -3111,22 +3306,22 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57">
-        <v>23330051920250</v>
+        <v>23330051920102</v>
       </c>
       <c r="B57" t="s">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="C57" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D57" t="s">
-        <v>221</v>
+        <v>252</v>
       </c>
       <c r="E57" t="s">
         <v>8</v>
       </c>
       <c r="F57" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G57">
         <v>1</v>
@@ -3134,22 +3329,22 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58">
-        <v>23330051920157</v>
+        <v>23330051920103</v>
       </c>
       <c r="B58" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C58" t="s">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="D58" t="s">
-        <v>222</v>
+        <v>253</v>
       </c>
       <c r="E58" t="s">
         <v>8</v>
       </c>
       <c r="F58" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G58">
         <v>1</v>
@@ -3157,22 +3352,22 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59">
-        <v>23330051920158</v>
+        <v>23330051920104</v>
       </c>
       <c r="B59" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="C59" t="s">
-        <v>70</v>
+        <v>154</v>
       </c>
       <c r="D59" t="s">
-        <v>223</v>
+        <v>254</v>
       </c>
       <c r="E59" t="s">
         <v>8</v>
       </c>
       <c r="F59" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G59">
         <v>1</v>
@@ -3180,22 +3375,22 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60">
-        <v>23330051920159</v>
+        <v>23330051920261</v>
       </c>
       <c r="B60" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C60" t="s">
-        <v>70</v>
+        <v>155</v>
       </c>
       <c r="D60" t="s">
-        <v>224</v>
+        <v>255</v>
       </c>
       <c r="E60" t="s">
         <v>8</v>
       </c>
       <c r="F60" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G60">
         <v>1</v>
@@ -3203,22 +3398,22 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61">
-        <v>23330051920163</v>
+        <v>23330051920106</v>
       </c>
       <c r="B61" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C61" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="D61" t="s">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="E61" t="s">
         <v>8</v>
       </c>
       <c r="F61" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G61">
         <v>1</v>
@@ -3226,22 +3421,22 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62">
-        <v>23330051920297</v>
+        <v>23330051920107</v>
       </c>
       <c r="B62" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="C62" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D62" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="E62" t="s">
         <v>8</v>
       </c>
       <c r="F62" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -3249,22 +3444,22 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63">
-        <v>23330051920167</v>
+        <v>23330051920108</v>
       </c>
       <c r="B63" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C63" t="s">
-        <v>86</v>
+        <v>157</v>
       </c>
       <c r="D63" t="s">
-        <v>227</v>
+        <v>258</v>
       </c>
       <c r="E63" t="s">
         <v>8</v>
       </c>
       <c r="F63" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G63">
         <v>1</v>
@@ -3272,22 +3467,22 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64">
-        <v>23330051920310</v>
+        <v>23330051920110</v>
       </c>
       <c r="B64" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C64" t="s">
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="D64" t="s">
-        <v>228</v>
+        <v>259</v>
       </c>
       <c r="E64" t="s">
         <v>8</v>
       </c>
       <c r="F64" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G64">
         <v>1</v>
@@ -3295,22 +3490,22 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65">
-        <v>23330051920169</v>
+        <v>23330051920111</v>
       </c>
       <c r="B65" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="C65" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="D65" t="s">
-        <v>229</v>
+        <v>260</v>
       </c>
       <c r="E65" t="s">
         <v>8</v>
       </c>
       <c r="F65" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G65">
         <v>1</v>
@@ -3318,22 +3513,22 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66">
-        <v>23330051920354</v>
+        <v>23330051920114</v>
       </c>
       <c r="B66" t="s">
-        <v>68</v>
+        <v>26</v>
       </c>
       <c r="C66" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="D66" t="s">
-        <v>230</v>
+        <v>261</v>
       </c>
       <c r="E66" t="s">
         <v>8</v>
       </c>
       <c r="F66" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G66">
         <v>1</v>
@@ -3341,22 +3536,22 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67">
-        <v>23330051920170</v>
+        <v>23330051920115</v>
       </c>
       <c r="B67" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C67" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="D67" t="s">
-        <v>231</v>
+        <v>262</v>
       </c>
       <c r="E67" t="s">
         <v>8</v>
       </c>
       <c r="F67" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G67">
         <v>1</v>
@@ -3364,16 +3559,16 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68">
-        <v>23330051920173</v>
+        <v>23330051920151</v>
       </c>
       <c r="B68" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C68" t="s">
-        <v>76</v>
+        <v>159</v>
       </c>
       <c r="D68" t="s">
-        <v>232</v>
+        <v>263</v>
       </c>
       <c r="E68" t="s">
         <v>8</v>
@@ -3387,16 +3582,16 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69">
-        <v>23330051920172</v>
+        <v>23330051920152</v>
       </c>
       <c r="B69" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C69" t="s">
-        <v>34</v>
+        <v>160</v>
       </c>
       <c r="D69" t="s">
-        <v>199</v>
+        <v>226</v>
       </c>
       <c r="E69" t="s">
         <v>8</v>
@@ -3410,16 +3605,16 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70">
-        <v>23330051920174</v>
+        <v>23330051920153</v>
       </c>
       <c r="B70" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C70" t="s">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="D70" t="s">
-        <v>233</v>
+        <v>264</v>
       </c>
       <c r="E70" t="s">
         <v>8</v>
@@ -3433,22 +3628,22 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71">
-        <v>23330051920048</v>
+        <v>23330051920155</v>
       </c>
       <c r="B71" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="C71" t="s">
-        <v>33</v>
+        <v>161</v>
       </c>
       <c r="D71" t="s">
-        <v>234</v>
+        <v>265</v>
       </c>
       <c r="E71" t="s">
         <v>8</v>
       </c>
       <c r="F71" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G71">
         <v>1</v>
@@ -3456,22 +3651,22 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72">
-        <v>23330051920050</v>
+        <v>23330051920154</v>
       </c>
       <c r="B72" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="C72" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="D72" t="s">
-        <v>235</v>
+        <v>266</v>
       </c>
       <c r="E72" t="s">
         <v>8</v>
       </c>
       <c r="F72" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G72">
         <v>1</v>
@@ -3479,22 +3674,22 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73">
-        <v>23330051920053</v>
+        <v>23330051920325</v>
       </c>
       <c r="B73" t="s">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="C73" t="s">
-        <v>127</v>
+        <v>162</v>
       </c>
       <c r="D73" t="s">
-        <v>236</v>
+        <v>267</v>
       </c>
       <c r="E73" t="s">
         <v>8</v>
       </c>
       <c r="F73" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G73">
         <v>1</v>
@@ -3502,22 +3697,22 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74">
-        <v>23330051920054</v>
+        <v>23330051920250</v>
       </c>
       <c r="B74" t="s">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="C74" t="s">
-        <v>23</v>
+        <v>103</v>
       </c>
       <c r="D74" t="s">
-        <v>237</v>
+        <v>268</v>
       </c>
       <c r="E74" t="s">
         <v>8</v>
       </c>
       <c r="F74" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G74">
         <v>1</v>
@@ -3525,22 +3720,22 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75">
-        <v>23330051920055</v>
+        <v>23330051920157</v>
       </c>
       <c r="B75" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="C75" t="s">
-        <v>140</v>
+        <v>25</v>
       </c>
       <c r="D75" t="s">
-        <v>238</v>
+        <v>269</v>
       </c>
       <c r="E75" t="s">
         <v>8</v>
       </c>
       <c r="F75" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G75">
         <v>1</v>
@@ -3548,22 +3743,22 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76">
-        <v>23330051920056</v>
+        <v>23330051920158</v>
       </c>
       <c r="B76" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="C76" t="s">
-        <v>49</v>
+        <v>83</v>
       </c>
       <c r="D76" t="s">
-        <v>239</v>
+        <v>270</v>
       </c>
       <c r="E76" t="s">
         <v>8</v>
       </c>
       <c r="F76" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G76">
         <v>1</v>
@@ -3571,22 +3766,22 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77">
-        <v>23330051920057</v>
+        <v>23330051920159</v>
       </c>
       <c r="B77" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="C77" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
       <c r="D77" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="E77" t="s">
         <v>8</v>
       </c>
       <c r="F77" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G77">
         <v>1</v>
@@ -3594,22 +3789,22 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78">
-        <v>23330051920058</v>
+        <v>23330051920160</v>
       </c>
       <c r="B78" t="s">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="C78" t="s">
-        <v>111</v>
+        <v>163</v>
       </c>
       <c r="D78" t="s">
-        <v>241</v>
+        <v>272</v>
       </c>
       <c r="E78" t="s">
         <v>8</v>
       </c>
       <c r="F78" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G78">
         <v>1</v>
@@ -3617,22 +3812,22 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79">
-        <v>23330051920060</v>
+        <v>23330051920161</v>
       </c>
       <c r="B79" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C79" t="s">
-        <v>34</v>
+        <v>164</v>
       </c>
       <c r="D79" t="s">
-        <v>242</v>
+        <v>273</v>
       </c>
       <c r="E79" t="s">
         <v>8</v>
       </c>
       <c r="F79" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G79">
         <v>1</v>
@@ -3640,22 +3835,22 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80">
-        <v>23330051920061</v>
+        <v>23330051920163</v>
       </c>
       <c r="B80" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="C80" t="s">
-        <v>141</v>
+        <v>165</v>
       </c>
       <c r="D80" t="s">
-        <v>243</v>
+        <v>274</v>
       </c>
       <c r="E80" t="s">
         <v>8</v>
       </c>
       <c r="F80" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G80">
         <v>1</v>
@@ -3663,22 +3858,22 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81">
-        <v>23330051920307</v>
+        <v>23330051920297</v>
       </c>
       <c r="B81" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C81" t="s">
-        <v>142</v>
+        <v>32</v>
       </c>
       <c r="D81" t="s">
-        <v>221</v>
+        <v>275</v>
       </c>
       <c r="E81" t="s">
         <v>8</v>
       </c>
       <c r="F81" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G81">
         <v>1</v>
@@ -3686,22 +3881,22 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82">
-        <v>23330051920063</v>
+        <v>23330051920165</v>
       </c>
       <c r="B82" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="C82" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D82" t="s">
-        <v>244</v>
+        <v>276</v>
       </c>
       <c r="E82" t="s">
         <v>8</v>
       </c>
       <c r="F82" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G82">
         <v>1</v>
@@ -3709,22 +3904,22 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83">
-        <v>23330051920064</v>
+        <v>23330051920166</v>
       </c>
       <c r="B83" t="s">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="C83" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D83" t="s">
-        <v>245</v>
+        <v>277</v>
       </c>
       <c r="E83" t="s">
         <v>8</v>
       </c>
       <c r="F83" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G83">
         <v>1</v>
@@ -3732,22 +3927,22 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84">
-        <v>23330051920066</v>
+        <v>23330051920167</v>
       </c>
       <c r="B84" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C84" t="s">
-        <v>114</v>
+        <v>25</v>
       </c>
       <c r="D84" t="s">
-        <v>246</v>
+        <v>278</v>
       </c>
       <c r="E84" t="s">
         <v>8</v>
       </c>
       <c r="F84" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G84">
         <v>1</v>
@@ -3755,22 +3950,22 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85">
-        <v>23330051920067</v>
+        <v>23330051920310</v>
       </c>
       <c r="B85" t="s">
-        <v>82</v>
+        <v>23</v>
       </c>
       <c r="C85" t="s">
-        <v>143</v>
+        <v>75</v>
       </c>
       <c r="D85" t="s">
-        <v>247</v>
+        <v>279</v>
       </c>
       <c r="E85" t="s">
         <v>8</v>
       </c>
       <c r="F85" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G85">
         <v>1</v>
@@ -3778,22 +3973,22 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86">
-        <v>23330051920068</v>
+        <v>23330051920169</v>
       </c>
       <c r="B86" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C86" t="s">
-        <v>144</v>
+        <v>90</v>
       </c>
       <c r="D86" t="s">
-        <v>248</v>
+        <v>280</v>
       </c>
       <c r="E86" t="s">
         <v>8</v>
       </c>
       <c r="F86" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G86">
         <v>1</v>
@@ -3801,22 +3996,22 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87">
-        <v>23330051920069</v>
+        <v>23330051920354</v>
       </c>
       <c r="B87" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C87" t="s">
-        <v>145</v>
+        <v>64</v>
       </c>
       <c r="D87" t="s">
-        <v>249</v>
+        <v>281</v>
       </c>
       <c r="E87" t="s">
         <v>8</v>
       </c>
       <c r="F87" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G87">
         <v>1</v>
@@ -3824,22 +4019,22 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88">
-        <v>23330051920070</v>
+        <v>23330051920170</v>
       </c>
       <c r="B88" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C88" t="s">
-        <v>32</v>
+        <v>166</v>
       </c>
       <c r="D88" t="s">
-        <v>250</v>
+        <v>282</v>
       </c>
       <c r="E88" t="s">
         <v>8</v>
       </c>
       <c r="F88" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G88">
         <v>1</v>
@@ -3847,22 +4042,22 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89">
-        <v>23330051920272</v>
+        <v>23330051920173</v>
       </c>
       <c r="B89" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C89" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="D89" t="s">
-        <v>251</v>
+        <v>283</v>
       </c>
       <c r="E89" t="s">
         <v>8</v>
       </c>
       <c r="F89" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G89">
         <v>1</v>
@@ -3870,22 +4065,22 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90">
-        <v>23330051920074</v>
+        <v>23330051920172</v>
       </c>
       <c r="B90" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C90" t="s">
-        <v>146</v>
+        <v>32</v>
       </c>
       <c r="D90" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="E90" t="s">
         <v>8</v>
       </c>
       <c r="F90" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G90">
         <v>1</v>
@@ -3893,22 +4088,22 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91">
-        <v>23330051920075</v>
+        <v>23330051920174</v>
       </c>
       <c r="B91" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C91" t="s">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="D91" t="s">
-        <v>253</v>
+        <v>284</v>
       </c>
       <c r="E91" t="s">
         <v>8</v>
       </c>
       <c r="F91" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G91">
         <v>1</v>
@@ -3916,22 +4111,22 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92">
-        <v>23330051920031</v>
+        <v>23330051920048</v>
       </c>
       <c r="B92" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C92" t="s">
-        <v>147</v>
+        <v>107</v>
       </c>
       <c r="D92" t="s">
-        <v>254</v>
+        <v>285</v>
       </c>
       <c r="E92" t="s">
         <v>8</v>
       </c>
       <c r="F92" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G92">
         <v>1</v>
@@ -3939,22 +4134,22 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93">
-        <v>23330051920033</v>
+        <v>23330051920049</v>
       </c>
       <c r="B93" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C93" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="D93" t="s">
-        <v>255</v>
+        <v>286</v>
       </c>
       <c r="E93" t="s">
         <v>8</v>
       </c>
       <c r="F93" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G93">
         <v>1</v>
@@ -3962,22 +4157,22 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94">
-        <v>23330051920034</v>
+        <v>23330051920050</v>
       </c>
       <c r="B94" t="s">
-        <v>51</v>
+        <v>88</v>
       </c>
       <c r="C94" t="s">
-        <v>27</v>
+        <v>168</v>
       </c>
       <c r="D94" t="s">
-        <v>256</v>
+        <v>287</v>
       </c>
       <c r="E94" t="s">
         <v>8</v>
       </c>
       <c r="F94" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G94">
         <v>1</v>
@@ -3985,22 +4180,22 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95">
-        <v>23330051920232</v>
+        <v>23330051920083</v>
       </c>
       <c r="B95" t="s">
+        <v>89</v>
+      </c>
+      <c r="C95" t="s">
         <v>91</v>
       </c>
-      <c r="C95" t="s">
-        <v>21</v>
-      </c>
       <c r="D95" t="s">
-        <v>257</v>
+        <v>288</v>
       </c>
       <c r="E95" t="s">
         <v>8</v>
       </c>
       <c r="F95" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G95">
         <v>1</v>
@@ -4008,22 +4203,22 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96">
-        <v>23330051920040</v>
+        <v>23330051920053</v>
       </c>
       <c r="B96" t="s">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="C96" t="s">
-        <v>95</v>
+        <v>148</v>
       </c>
       <c r="D96" t="s">
-        <v>258</v>
+        <v>289</v>
       </c>
       <c r="E96" t="s">
         <v>8</v>
       </c>
       <c r="F96" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G96">
         <v>1</v>
@@ -4031,22 +4226,22 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97">
-        <v>23330051920041</v>
+        <v>23330051920054</v>
       </c>
       <c r="B97" t="s">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="C97" t="s">
-        <v>149</v>
+        <v>27</v>
       </c>
       <c r="D97" t="s">
-        <v>259</v>
+        <v>290</v>
       </c>
       <c r="E97" t="s">
         <v>8</v>
       </c>
       <c r="F97" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G97">
         <v>1</v>
@@ -4054,22 +4249,22 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98">
-        <v>23330051920042</v>
+        <v>23330051920055</v>
       </c>
       <c r="B98" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C98" t="s">
-        <v>21</v>
+        <v>169</v>
       </c>
       <c r="D98" t="s">
-        <v>260</v>
+        <v>291</v>
       </c>
       <c r="E98" t="s">
         <v>8</v>
       </c>
       <c r="F98" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G98">
         <v>1</v>
@@ -4077,22 +4272,22 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99">
-        <v>23330051920043</v>
+        <v>23330051920056</v>
       </c>
       <c r="B99" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C99" t="s">
-        <v>123</v>
+        <v>35</v>
       </c>
       <c r="D99" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="E99" t="s">
         <v>8</v>
       </c>
       <c r="F99" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G99">
         <v>1</v>
@@ -4100,22 +4295,22 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100">
-        <v>23330051920044</v>
+        <v>23330051920057</v>
       </c>
       <c r="B100" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C100" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="D100" t="s">
-        <v>262</v>
+        <v>293</v>
       </c>
       <c r="E100" t="s">
         <v>8</v>
       </c>
       <c r="F100" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G100">
         <v>1</v>
@@ -4123,22 +4318,22 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101">
-        <v>23330051920209</v>
+        <v>23330051920058</v>
       </c>
       <c r="B101" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C101" t="s">
-        <v>150</v>
+        <v>36</v>
       </c>
       <c r="D101" t="s">
-        <v>263</v>
+        <v>294</v>
       </c>
       <c r="E101" t="s">
         <v>8</v>
       </c>
       <c r="F101" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G101">
         <v>1</v>
@@ -4146,22 +4341,22 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102">
-        <v>23330051920046</v>
+        <v>23330051920246</v>
       </c>
       <c r="B102" t="s">
-        <v>96</v>
+        <v>49</v>
       </c>
       <c r="C102" t="s">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="D102" t="s">
-        <v>264</v>
+        <v>295</v>
       </c>
       <c r="E102" t="s">
         <v>8</v>
       </c>
       <c r="F102" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G102">
         <v>1</v>
@@ -4169,22 +4364,22 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103">
-        <v>23330051920117</v>
+        <v>23330051920060</v>
       </c>
       <c r="B103" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C103" t="s">
-        <v>152</v>
+        <v>32</v>
       </c>
       <c r="D103" t="s">
-        <v>265</v>
+        <v>296</v>
       </c>
       <c r="E103" t="s">
         <v>8</v>
       </c>
       <c r="F103" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G103">
         <v>1</v>
@@ -4192,22 +4387,22 @@
     </row>
     <row r="104" spans="1:7">
       <c r="A104">
-        <v>23330061460223</v>
+        <v>23330051920061</v>
       </c>
       <c r="B104" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C104" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D104" t="s">
-        <v>266</v>
+        <v>297</v>
       </c>
       <c r="E104" t="s">
         <v>8</v>
       </c>
       <c r="F104" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G104">
         <v>1</v>
@@ -4215,22 +4410,22 @@
     </row>
     <row r="105" spans="1:7">
       <c r="A105">
-        <v>23330051920119</v>
+        <v>23330051920062</v>
       </c>
       <c r="B105" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C105" t="s">
-        <v>154</v>
+        <v>49</v>
       </c>
       <c r="D105" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="E105" t="s">
         <v>8</v>
       </c>
       <c r="F105" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G105">
         <v>1</v>
@@ -4238,13 +4433,13 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106">
-        <v>23330051920120</v>
+        <v>23330051920307</v>
       </c>
       <c r="B106" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C106" t="s">
-        <v>35</v>
+        <v>172</v>
       </c>
       <c r="D106" t="s">
         <v>268</v>
@@ -4253,7 +4448,7 @@
         <v>8</v>
       </c>
       <c r="F106" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G106">
         <v>1</v>
@@ -4261,22 +4456,22 @@
     </row>
     <row r="107" spans="1:7">
       <c r="A107">
-        <v>23330051920121</v>
+        <v>23330051920063</v>
       </c>
       <c r="B107" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="C107" t="s">
-        <v>155</v>
+        <v>28</v>
       </c>
       <c r="D107" t="s">
-        <v>235</v>
+        <v>298</v>
       </c>
       <c r="E107" t="s">
         <v>8</v>
       </c>
       <c r="F107" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G107">
         <v>1</v>
@@ -4284,22 +4479,22 @@
     </row>
     <row r="108" spans="1:7">
       <c r="A108">
-        <v>23330051920124</v>
+        <v>23330051920064</v>
       </c>
       <c r="B108" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="C108" t="s">
-        <v>156</v>
+        <v>25</v>
       </c>
       <c r="D108" t="s">
-        <v>269</v>
+        <v>299</v>
       </c>
       <c r="E108" t="s">
         <v>8</v>
       </c>
       <c r="F108" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G108">
         <v>1</v>
@@ -4307,22 +4502,22 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109">
-        <v>23330051920125</v>
+        <v>23330051920259</v>
       </c>
       <c r="B109" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="C109" t="s">
-        <v>115</v>
+        <v>173</v>
       </c>
       <c r="D109" t="s">
-        <v>270</v>
+        <v>300</v>
       </c>
       <c r="E109" t="s">
         <v>8</v>
       </c>
       <c r="F109" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G109">
         <v>1</v>
@@ -4330,22 +4525,22 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110">
-        <v>23330051920126</v>
+        <v>23330051920065</v>
       </c>
       <c r="B110" t="s">
-        <v>102</v>
+        <v>29</v>
       </c>
       <c r="C110" t="s">
-        <v>70</v>
+        <v>174</v>
       </c>
       <c r="D110" t="s">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="E110" t="s">
         <v>8</v>
       </c>
       <c r="F110" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G110">
         <v>1</v>
@@ -4353,22 +4548,22 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111">
-        <v>23330051920127</v>
+        <v>23330051920263</v>
       </c>
       <c r="B111" t="s">
-        <v>27</v>
+        <v>98</v>
       </c>
       <c r="C111" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="D111" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="E111" t="s">
         <v>8</v>
       </c>
       <c r="F111" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G111">
         <v>1</v>
@@ -4376,22 +4571,22 @@
     </row>
     <row r="112" spans="1:7">
       <c r="A112">
-        <v>23330051920128</v>
+        <v>23330051920066</v>
       </c>
       <c r="B112" t="s">
-        <v>27</v>
+        <v>99</v>
       </c>
       <c r="C112" t="s">
-        <v>35</v>
+        <v>164</v>
       </c>
       <c r="D112" t="s">
-        <v>273</v>
+        <v>303</v>
       </c>
       <c r="E112" t="s">
         <v>8</v>
       </c>
       <c r="F112" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G112">
         <v>1</v>
@@ -4399,22 +4594,22 @@
     </row>
     <row r="113" spans="1:7">
       <c r="A113">
-        <v>23330051920129</v>
+        <v>23330051920067</v>
       </c>
       <c r="B113" t="s">
-        <v>27</v>
+        <v>100</v>
       </c>
       <c r="C113" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="D113" t="s">
-        <v>274</v>
+        <v>304</v>
       </c>
       <c r="E113" t="s">
         <v>8</v>
       </c>
       <c r="F113" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G113">
         <v>1</v>
@@ -4422,22 +4617,22 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114">
-        <v>23330051920130</v>
+        <v>23330051920068</v>
       </c>
       <c r="B114" t="s">
-        <v>27</v>
+        <v>101</v>
       </c>
       <c r="C114" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="D114" t="s">
-        <v>275</v>
+        <v>305</v>
       </c>
       <c r="E114" t="s">
         <v>8</v>
       </c>
       <c r="F114" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G114">
         <v>1</v>
@@ -4445,22 +4640,22 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115">
-        <v>23330051920134</v>
+        <v>23330051920069</v>
       </c>
       <c r="B115" t="s">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="C115" t="s">
-        <v>27</v>
+        <v>177</v>
       </c>
       <c r="D115" t="s">
-        <v>276</v>
+        <v>306</v>
       </c>
       <c r="E115" t="s">
         <v>8</v>
       </c>
       <c r="F115" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G115">
         <v>1</v>
@@ -4468,22 +4663,22 @@
     </row>
     <row r="116" spans="1:7">
       <c r="A116">
-        <v>23330051920135</v>
+        <v>23330051920070</v>
       </c>
       <c r="B116" t="s">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="C116" t="s">
-        <v>121</v>
+        <v>37</v>
       </c>
       <c r="D116" t="s">
-        <v>277</v>
+        <v>307</v>
       </c>
       <c r="E116" t="s">
         <v>8</v>
       </c>
       <c r="F116" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G116">
         <v>1</v>
@@ -4491,22 +4686,22 @@
     </row>
     <row r="117" spans="1:7">
       <c r="A117">
-        <v>23330051920137</v>
+        <v>23330051920272</v>
       </c>
       <c r="B117" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="C117" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="D117" t="s">
-        <v>278</v>
+        <v>308</v>
       </c>
       <c r="E117" t="s">
         <v>8</v>
       </c>
       <c r="F117" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G117">
         <v>1</v>
@@ -4514,22 +4709,22 @@
     </row>
     <row r="118" spans="1:7">
       <c r="A118">
-        <v>23330051920122</v>
+        <v>23330051920071</v>
       </c>
       <c r="B118" t="s">
+        <v>25</v>
+      </c>
+      <c r="C118" t="s">
         <v>35</v>
       </c>
-      <c r="C118" t="s">
-        <v>160</v>
-      </c>
       <c r="D118" t="s">
-        <v>279</v>
+        <v>309</v>
       </c>
       <c r="E118" t="s">
         <v>8</v>
       </c>
       <c r="F118" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G118">
         <v>1</v>
@@ -4537,22 +4732,22 @@
     </row>
     <row r="119" spans="1:7">
       <c r="A119">
-        <v>23330051920140</v>
+        <v>23330051920074</v>
       </c>
       <c r="B119" t="s">
         <v>104</v>
       </c>
       <c r="C119" t="s">
-        <v>115</v>
+        <v>178</v>
       </c>
       <c r="D119" t="s">
-        <v>280</v>
+        <v>310</v>
       </c>
       <c r="E119" t="s">
         <v>8</v>
       </c>
       <c r="F119" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G119">
         <v>1</v>
@@ -4560,22 +4755,22 @@
     </row>
     <row r="120" spans="1:7">
       <c r="A120">
-        <v>23330051920138</v>
+        <v>23330051920075</v>
       </c>
       <c r="B120" t="s">
         <v>105</v>
       </c>
       <c r="C120" t="s">
-        <v>161</v>
+        <v>27</v>
       </c>
       <c r="D120" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="E120" t="s">
         <v>8</v>
       </c>
       <c r="F120" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G120">
         <v>1</v>
@@ -4583,22 +4778,22 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121">
-        <v>23330051920255</v>
+        <v>23330051920029</v>
       </c>
       <c r="B121" t="s">
-        <v>106</v>
+        <v>37</v>
       </c>
       <c r="C121" t="s">
-        <v>162</v>
+        <v>21</v>
       </c>
       <c r="D121" t="s">
-        <v>282</v>
+        <v>312</v>
       </c>
       <c r="E121" t="s">
         <v>8</v>
       </c>
       <c r="F121" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G121">
         <v>1</v>
@@ -4606,22 +4801,22 @@
     </row>
     <row r="122" spans="1:7">
       <c r="A122">
-        <v>23330051920315</v>
+        <v>23330051920031</v>
       </c>
       <c r="B122" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C122" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="D122" t="s">
-        <v>283</v>
+        <v>313</v>
       </c>
       <c r="E122" t="s">
         <v>8</v>
       </c>
       <c r="F122" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G122">
         <v>1</v>
@@ -4629,22 +4824,22 @@
     </row>
     <row r="123" spans="1:7">
       <c r="A123">
-        <v>23330051920143</v>
+        <v>23330051920030</v>
       </c>
       <c r="B123" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C123" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="D123" t="s">
-        <v>284</v>
+        <v>314</v>
       </c>
       <c r="E123" t="s">
         <v>8</v>
       </c>
       <c r="F123" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G123">
         <v>1</v>
@@ -4652,22 +4847,22 @@
     </row>
     <row r="124" spans="1:7">
       <c r="A124">
-        <v>23330051920144</v>
+        <v>23330051920033</v>
       </c>
       <c r="B124" t="s">
-        <v>44</v>
+        <v>108</v>
       </c>
       <c r="C124" t="s">
-        <v>44</v>
+        <v>181</v>
       </c>
       <c r="D124" t="s">
-        <v>285</v>
+        <v>315</v>
       </c>
       <c r="E124" t="s">
         <v>8</v>
       </c>
       <c r="F124" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G124">
         <v>1</v>
@@ -4675,22 +4870,22 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125">
-        <v>23330051920146</v>
+        <v>23330051920034</v>
       </c>
       <c r="B125" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="C125" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D125" t="s">
-        <v>286</v>
+        <v>316</v>
       </c>
       <c r="E125" t="s">
         <v>8</v>
       </c>
       <c r="F125" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G125">
         <v>1</v>
@@ -4698,22 +4893,22 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126">
-        <v>23330051920147</v>
+        <v>23330051920232</v>
       </c>
       <c r="B126" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="C126" t="s">
-        <v>165</v>
+        <v>48</v>
       </c>
       <c r="D126" t="s">
-        <v>287</v>
+        <v>302</v>
       </c>
       <c r="E126" t="s">
         <v>8</v>
       </c>
       <c r="F126" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G126">
         <v>1</v>
@@ -4721,22 +4916,22 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127">
-        <v>23330051920346</v>
+        <v>23330051920035</v>
       </c>
       <c r="B127" t="s">
-        <v>107</v>
+        <v>28</v>
       </c>
       <c r="C127" t="s">
-        <v>50</v>
+        <v>96</v>
       </c>
       <c r="D127" t="s">
-        <v>288</v>
+        <v>317</v>
       </c>
       <c r="E127" t="s">
         <v>8</v>
       </c>
       <c r="F127" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G127">
         <v>1</v>
@@ -4744,22 +4939,22 @@
     </row>
     <row r="128" spans="1:7">
       <c r="A128">
-        <v>23330051920149</v>
+        <v>23330051920037</v>
       </c>
       <c r="B128" t="s">
-        <v>108</v>
+        <v>32</v>
       </c>
       <c r="C128" t="s">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="D128" t="s">
-        <v>289</v>
+        <v>318</v>
       </c>
       <c r="E128" t="s">
         <v>8</v>
       </c>
       <c r="F128" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G128">
         <v>1</v>
@@ -4767,24 +4962,898 @@
     </row>
     <row r="129" spans="1:7">
       <c r="A129">
+        <v>23330051920032</v>
+      </c>
+      <c r="B129" t="s">
+        <v>110</v>
+      </c>
+      <c r="C129" t="s">
+        <v>39</v>
+      </c>
+      <c r="D129" t="s">
+        <v>319</v>
+      </c>
+      <c r="E129" t="s">
+        <v>8</v>
+      </c>
+      <c r="F129" t="s">
+        <v>12</v>
+      </c>
+      <c r="G129">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7">
+      <c r="A130">
+        <v>22330051920021</v>
+      </c>
+      <c r="B130" t="s">
+        <v>111</v>
+      </c>
+      <c r="C130" t="s">
+        <v>48</v>
+      </c>
+      <c r="D130" t="s">
+        <v>320</v>
+      </c>
+      <c r="E130" t="s">
+        <v>8</v>
+      </c>
+      <c r="F130" t="s">
+        <v>12</v>
+      </c>
+      <c r="G130">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7">
+      <c r="A131">
+        <v>23330051920040</v>
+      </c>
+      <c r="B131" t="s">
+        <v>112</v>
+      </c>
+      <c r="C131" t="s">
+        <v>115</v>
+      </c>
+      <c r="D131" t="s">
+        <v>321</v>
+      </c>
+      <c r="E131" t="s">
+        <v>8</v>
+      </c>
+      <c r="F131" t="s">
+        <v>12</v>
+      </c>
+      <c r="G131">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7">
+      <c r="A132">
+        <v>23330051920041</v>
+      </c>
+      <c r="B132" t="s">
+        <v>63</v>
+      </c>
+      <c r="C132" t="s">
+        <v>183</v>
+      </c>
+      <c r="D132" t="s">
+        <v>322</v>
+      </c>
+      <c r="E132" t="s">
+        <v>8</v>
+      </c>
+      <c r="F132" t="s">
+        <v>12</v>
+      </c>
+      <c r="G132">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7">
+      <c r="A133">
+        <v>23330051920042</v>
+      </c>
+      <c r="B133" t="s">
+        <v>113</v>
+      </c>
+      <c r="C133" t="s">
+        <v>48</v>
+      </c>
+      <c r="D133" t="s">
+        <v>323</v>
+      </c>
+      <c r="E133" t="s">
+        <v>8</v>
+      </c>
+      <c r="F133" t="s">
+        <v>12</v>
+      </c>
+      <c r="G133">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7">
+      <c r="A134">
+        <v>23330051920043</v>
+      </c>
+      <c r="B134" t="s">
+        <v>25</v>
+      </c>
+      <c r="C134" t="s">
+        <v>143</v>
+      </c>
+      <c r="D134" t="s">
+        <v>324</v>
+      </c>
+      <c r="E134" t="s">
+        <v>8</v>
+      </c>
+      <c r="F134" t="s">
+        <v>12</v>
+      </c>
+      <c r="G134">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7">
+      <c r="A135">
+        <v>23330051920044</v>
+      </c>
+      <c r="B135" t="s">
+        <v>114</v>
+      </c>
+      <c r="C135" t="s">
+        <v>62</v>
+      </c>
+      <c r="D135" t="s">
+        <v>325</v>
+      </c>
+      <c r="E135" t="s">
+        <v>8</v>
+      </c>
+      <c r="F135" t="s">
+        <v>12</v>
+      </c>
+      <c r="G135">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7">
+      <c r="A136">
+        <v>23330051920209</v>
+      </c>
+      <c r="B136" t="s">
+        <v>115</v>
+      </c>
+      <c r="C136" t="s">
+        <v>184</v>
+      </c>
+      <c r="D136" t="s">
+        <v>326</v>
+      </c>
+      <c r="E136" t="s">
+        <v>8</v>
+      </c>
+      <c r="F136" t="s">
+        <v>12</v>
+      </c>
+      <c r="G136">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7">
+      <c r="A137">
+        <v>23330051920046</v>
+      </c>
+      <c r="B137" t="s">
+        <v>116</v>
+      </c>
+      <c r="C137" t="s">
+        <v>185</v>
+      </c>
+      <c r="D137" t="s">
+        <v>327</v>
+      </c>
+      <c r="E137" t="s">
+        <v>8</v>
+      </c>
+      <c r="F137" t="s">
+        <v>12</v>
+      </c>
+      <c r="G137">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7">
+      <c r="A138">
+        <v>23330051920117</v>
+      </c>
+      <c r="B138" t="s">
+        <v>117</v>
+      </c>
+      <c r="C138" t="s">
+        <v>186</v>
+      </c>
+      <c r="D138" t="s">
+        <v>328</v>
+      </c>
+      <c r="E138" t="s">
+        <v>8</v>
+      </c>
+      <c r="F138" t="s">
+        <v>13</v>
+      </c>
+      <c r="G138">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7">
+      <c r="A139">
+        <v>23330061460223</v>
+      </c>
+      <c r="B139" t="s">
+        <v>118</v>
+      </c>
+      <c r="C139" t="s">
+        <v>136</v>
+      </c>
+      <c r="D139" t="s">
+        <v>329</v>
+      </c>
+      <c r="E139" t="s">
+        <v>8</v>
+      </c>
+      <c r="F139" t="s">
+        <v>13</v>
+      </c>
+      <c r="G139">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7">
+      <c r="A140">
+        <v>23330051920119</v>
+      </c>
+      <c r="B140" t="s">
+        <v>119</v>
+      </c>
+      <c r="C140" t="s">
+        <v>187</v>
+      </c>
+      <c r="D140" t="s">
+        <v>330</v>
+      </c>
+      <c r="E140" t="s">
+        <v>8</v>
+      </c>
+      <c r="F140" t="s">
+        <v>13</v>
+      </c>
+      <c r="G140">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7">
+      <c r="A141">
+        <v>23330051920120</v>
+      </c>
+      <c r="B141" t="s">
+        <v>120</v>
+      </c>
+      <c r="C141" t="s">
+        <v>110</v>
+      </c>
+      <c r="D141" t="s">
+        <v>331</v>
+      </c>
+      <c r="E141" t="s">
+        <v>8</v>
+      </c>
+      <c r="F141" t="s">
+        <v>13</v>
+      </c>
+      <c r="G141">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7">
+      <c r="A142">
+        <v>23330051920121</v>
+      </c>
+      <c r="B142" t="s">
+        <v>121</v>
+      </c>
+      <c r="C142" t="s">
+        <v>188</v>
+      </c>
+      <c r="D142" t="s">
+        <v>287</v>
+      </c>
+      <c r="E142" t="s">
+        <v>8</v>
+      </c>
+      <c r="F142" t="s">
+        <v>13</v>
+      </c>
+      <c r="G142">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7">
+      <c r="A143">
+        <v>23330051920124</v>
+      </c>
+      <c r="B143" t="s">
+        <v>49</v>
+      </c>
+      <c r="C143" t="s">
+        <v>189</v>
+      </c>
+      <c r="D143" t="s">
+        <v>332</v>
+      </c>
+      <c r="E143" t="s">
+        <v>8</v>
+      </c>
+      <c r="F143" t="s">
+        <v>13</v>
+      </c>
+      <c r="G143">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7">
+      <c r="A144">
+        <v>23330051920125</v>
+      </c>
+      <c r="B144" t="s">
+        <v>21</v>
+      </c>
+      <c r="C144" t="s">
+        <v>174</v>
+      </c>
+      <c r="D144" t="s">
+        <v>333</v>
+      </c>
+      <c r="E144" t="s">
+        <v>8</v>
+      </c>
+      <c r="F144" t="s">
+        <v>13</v>
+      </c>
+      <c r="G144">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7">
+      <c r="A145">
+        <v>23330051920126</v>
+      </c>
+      <c r="B145" t="s">
+        <v>122</v>
+      </c>
+      <c r="C145" t="s">
+        <v>83</v>
+      </c>
+      <c r="D145" t="s">
+        <v>334</v>
+      </c>
+      <c r="E145" t="s">
+        <v>8</v>
+      </c>
+      <c r="F145" t="s">
+        <v>13</v>
+      </c>
+      <c r="G145">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7">
+      <c r="A146">
+        <v>23330051920127</v>
+      </c>
+      <c r="B146" t="s">
+        <v>28</v>
+      </c>
+      <c r="C146" t="s">
+        <v>162</v>
+      </c>
+      <c r="D146" t="s">
+        <v>335</v>
+      </c>
+      <c r="E146" t="s">
+        <v>8</v>
+      </c>
+      <c r="F146" t="s">
+        <v>13</v>
+      </c>
+      <c r="G146">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7">
+      <c r="A147">
+        <v>23330051920128</v>
+      </c>
+      <c r="B147" t="s">
+        <v>28</v>
+      </c>
+      <c r="C147" t="s">
+        <v>110</v>
+      </c>
+      <c r="D147" t="s">
+        <v>336</v>
+      </c>
+      <c r="E147" t="s">
+        <v>8</v>
+      </c>
+      <c r="F147" t="s">
+        <v>13</v>
+      </c>
+      <c r="G147">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7">
+      <c r="A148">
+        <v>23330051920129</v>
+      </c>
+      <c r="B148" t="s">
+        <v>28</v>
+      </c>
+      <c r="C148" t="s">
+        <v>64</v>
+      </c>
+      <c r="D148" t="s">
+        <v>337</v>
+      </c>
+      <c r="E148" t="s">
+        <v>8</v>
+      </c>
+      <c r="F148" t="s">
+        <v>13</v>
+      </c>
+      <c r="G148">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7">
+      <c r="A149">
+        <v>23330051920130</v>
+      </c>
+      <c r="B149" t="s">
+        <v>28</v>
+      </c>
+      <c r="C149" t="s">
+        <v>190</v>
+      </c>
+      <c r="D149" t="s">
+        <v>338</v>
+      </c>
+      <c r="E149" t="s">
+        <v>8</v>
+      </c>
+      <c r="F149" t="s">
+        <v>13</v>
+      </c>
+      <c r="G149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7">
+      <c r="A150">
+        <v>23330051920133</v>
+      </c>
+      <c r="B150" t="s">
+        <v>95</v>
+      </c>
+      <c r="C150" t="s">
+        <v>100</v>
+      </c>
+      <c r="D150" t="s">
+        <v>339</v>
+      </c>
+      <c r="E150" t="s">
+        <v>8</v>
+      </c>
+      <c r="F150" t="s">
+        <v>13</v>
+      </c>
+      <c r="G150">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7">
+      <c r="A151">
+        <v>23330051920134</v>
+      </c>
+      <c r="B151" t="s">
+        <v>32</v>
+      </c>
+      <c r="C151" t="s">
+        <v>28</v>
+      </c>
+      <c r="D151" t="s">
+        <v>340</v>
+      </c>
+      <c r="E151" t="s">
+        <v>8</v>
+      </c>
+      <c r="F151" t="s">
+        <v>13</v>
+      </c>
+      <c r="G151">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7">
+      <c r="A152">
+        <v>23330051920135</v>
+      </c>
+      <c r="B152" t="s">
+        <v>32</v>
+      </c>
+      <c r="C152" t="s">
+        <v>140</v>
+      </c>
+      <c r="D152" t="s">
+        <v>341</v>
+      </c>
+      <c r="E152" t="s">
+        <v>8</v>
+      </c>
+      <c r="F152" t="s">
+        <v>13</v>
+      </c>
+      <c r="G152">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7">
+      <c r="A153">
+        <v>23330051920137</v>
+      </c>
+      <c r="B153" t="s">
+        <v>123</v>
+      </c>
+      <c r="C153" t="s">
+        <v>191</v>
+      </c>
+      <c r="D153" t="s">
+        <v>208</v>
+      </c>
+      <c r="E153" t="s">
+        <v>8</v>
+      </c>
+      <c r="F153" t="s">
+        <v>13</v>
+      </c>
+      <c r="G153">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7">
+      <c r="A154">
+        <v>23330051920122</v>
+      </c>
+      <c r="B154" t="s">
+        <v>110</v>
+      </c>
+      <c r="C154" t="s">
+        <v>192</v>
+      </c>
+      <c r="D154" t="s">
+        <v>342</v>
+      </c>
+      <c r="E154" t="s">
+        <v>8</v>
+      </c>
+      <c r="F154" t="s">
+        <v>13</v>
+      </c>
+      <c r="G154">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7">
+      <c r="A155">
+        <v>23330051920140</v>
+      </c>
+      <c r="B155" t="s">
+        <v>124</v>
+      </c>
+      <c r="C155" t="s">
+        <v>174</v>
+      </c>
+      <c r="D155" t="s">
+        <v>343</v>
+      </c>
+      <c r="E155" t="s">
+        <v>8</v>
+      </c>
+      <c r="F155" t="s">
+        <v>13</v>
+      </c>
+      <c r="G155">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7">
+      <c r="A156">
+        <v>23330051920139</v>
+      </c>
+      <c r="B156" t="s">
+        <v>77</v>
+      </c>
+      <c r="C156" t="s">
+        <v>80</v>
+      </c>
+      <c r="D156" t="s">
+        <v>344</v>
+      </c>
+      <c r="E156" t="s">
+        <v>8</v>
+      </c>
+      <c r="F156" t="s">
+        <v>13</v>
+      </c>
+      <c r="G156">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7">
+      <c r="A157">
+        <v>23330051920138</v>
+      </c>
+      <c r="B157" t="s">
+        <v>125</v>
+      </c>
+      <c r="C157" t="s">
+        <v>193</v>
+      </c>
+      <c r="D157" t="s">
+        <v>345</v>
+      </c>
+      <c r="E157" t="s">
+        <v>8</v>
+      </c>
+      <c r="F157" t="s">
+        <v>13</v>
+      </c>
+      <c r="G157">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7">
+      <c r="A158">
+        <v>23330051920255</v>
+      </c>
+      <c r="B158" t="s">
+        <v>126</v>
+      </c>
+      <c r="C158" t="s">
+        <v>194</v>
+      </c>
+      <c r="D158" t="s">
+        <v>346</v>
+      </c>
+      <c r="E158" t="s">
+        <v>8</v>
+      </c>
+      <c r="F158" t="s">
+        <v>13</v>
+      </c>
+      <c r="G158">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7">
+      <c r="A159">
+        <v>23330051920141</v>
+      </c>
+      <c r="B159" t="s">
+        <v>29</v>
+      </c>
+      <c r="C159" t="s">
+        <v>195</v>
+      </c>
+      <c r="D159" t="s">
+        <v>347</v>
+      </c>
+      <c r="E159" t="s">
+        <v>8</v>
+      </c>
+      <c r="F159" t="s">
+        <v>13</v>
+      </c>
+      <c r="G159">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7">
+      <c r="A160">
+        <v>23330051920315</v>
+      </c>
+      <c r="B160" t="s">
+        <v>103</v>
+      </c>
+      <c r="C160" t="s">
+        <v>196</v>
+      </c>
+      <c r="D160" t="s">
+        <v>348</v>
+      </c>
+      <c r="E160" t="s">
+        <v>8</v>
+      </c>
+      <c r="F160" t="s">
+        <v>13</v>
+      </c>
+      <c r="G160">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7">
+      <c r="A161">
+        <v>23330051920143</v>
+      </c>
+      <c r="B161" t="s">
+        <v>25</v>
+      </c>
+      <c r="C161" t="s">
+        <v>138</v>
+      </c>
+      <c r="D161" t="s">
+        <v>349</v>
+      </c>
+      <c r="E161" t="s">
+        <v>8</v>
+      </c>
+      <c r="F161" t="s">
+        <v>13</v>
+      </c>
+      <c r="G161">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7">
+      <c r="A162">
+        <v>23330051920145</v>
+      </c>
+      <c r="B162" t="s">
+        <v>127</v>
+      </c>
+      <c r="C162" t="s">
+        <v>83</v>
+      </c>
+      <c r="D162" t="s">
+        <v>350</v>
+      </c>
+      <c r="E162" t="s">
+        <v>8</v>
+      </c>
+      <c r="F162" t="s">
+        <v>13</v>
+      </c>
+      <c r="G162">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7">
+      <c r="A163">
+        <v>23330051920146</v>
+      </c>
+      <c r="B163" t="s">
+        <v>83</v>
+      </c>
+      <c r="C163" t="s">
+        <v>21</v>
+      </c>
+      <c r="D163" t="s">
+        <v>351</v>
+      </c>
+      <c r="E163" t="s">
+        <v>8</v>
+      </c>
+      <c r="F163" t="s">
+        <v>13</v>
+      </c>
+      <c r="G163">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7">
+      <c r="A164">
+        <v>23330051920147</v>
+      </c>
+      <c r="B164" t="s">
+        <v>115</v>
+      </c>
+      <c r="C164" t="s">
+        <v>197</v>
+      </c>
+      <c r="D164" t="s">
+        <v>352</v>
+      </c>
+      <c r="E164" t="s">
+        <v>8</v>
+      </c>
+      <c r="F164" t="s">
+        <v>13</v>
+      </c>
+      <c r="G164">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7">
+      <c r="A165">
+        <v>23330051920346</v>
+      </c>
+      <c r="B165" t="s">
+        <v>128</v>
+      </c>
+      <c r="C165" t="s">
+        <v>59</v>
+      </c>
+      <c r="D165" t="s">
+        <v>353</v>
+      </c>
+      <c r="E165" t="s">
+        <v>8</v>
+      </c>
+      <c r="F165" t="s">
+        <v>13</v>
+      </c>
+      <c r="G165">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7">
+      <c r="A166">
+        <v>23330051920149</v>
+      </c>
+      <c r="B166" t="s">
+        <v>129</v>
+      </c>
+      <c r="C166" t="s">
+        <v>198</v>
+      </c>
+      <c r="D166" t="s">
+        <v>354</v>
+      </c>
+      <c r="E166" t="s">
+        <v>8</v>
+      </c>
+      <c r="F166" t="s">
+        <v>13</v>
+      </c>
+      <c r="G166">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7">
+      <c r="A167">
         <v>23330051920150</v>
       </c>
-      <c r="B129" t="s">
-        <v>109</v>
-      </c>
-      <c r="C129" t="s">
-        <v>25</v>
-      </c>
-      <c r="D129" t="s">
-        <v>290</v>
-      </c>
-      <c r="E129" t="s">
-        <v>8</v>
-      </c>
-      <c r="F129" t="s">
+      <c r="B167" t="s">
+        <v>130</v>
+      </c>
+      <c r="C167" t="s">
+        <v>24</v>
+      </c>
+      <c r="D167" t="s">
+        <v>355</v>
+      </c>
+      <c r="E167" t="s">
+        <v>8</v>
+      </c>
+      <c r="F167" t="s">
         <v>13</v>
       </c>
-      <c r="G129">
+      <c r="G167">
         <v>1</v>
       </c>
     </row>
